--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124835238</v>
+        <v>124838321</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609369</v>
+        <v>609213</v>
       </c>
       <c r="R3" t="n">
-        <v>7018099</v>
+        <v>7018126</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124838321</v>
+        <v>124835238</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609213</v>
+        <v>609369</v>
       </c>
       <c r="R4" t="n">
-        <v>7018126</v>
+        <v>7018099</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124834152</v>
+        <v>124834208</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609537</v>
+        <v>609480</v>
       </c>
       <c r="R13" t="n">
-        <v>7018055</v>
+        <v>7018081</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124834208</v>
+        <v>124838441</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609480</v>
+        <v>609200</v>
       </c>
       <c r="R14" t="n">
-        <v>7018081</v>
+        <v>7018089</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838441</v>
+        <v>124834152</v>
       </c>
       <c r="B15" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2021,25 +2021,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609200</v>
+        <v>609537</v>
       </c>
       <c r="R15" t="n">
-        <v>7018089</v>
+        <v>7018055</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -3253,6 +3253,112 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124835191</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91705</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>67</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>609354</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7018124</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838321</v>
+        <v>124834152</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609213</v>
+        <v>609537</v>
       </c>
       <c r="R3" t="n">
-        <v>7018126</v>
+        <v>7018055</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124835238</v>
+        <v>124835224</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609369</v>
+        <v>609360</v>
       </c>
       <c r="R4" t="n">
-        <v>7018099</v>
+        <v>7018113</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124835224</v>
+        <v>124838200</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609360</v>
+        <v>609219</v>
       </c>
       <c r="R5" t="n">
-        <v>7018113</v>
+        <v>7018134</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124838200</v>
+        <v>124834267</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1099,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609219</v>
+        <v>609474</v>
       </c>
       <c r="R6" t="n">
-        <v>7018134</v>
+        <v>7018096</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838495</v>
+        <v>124838262</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1205,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609194</v>
+        <v>609214</v>
       </c>
       <c r="R7" t="n">
-        <v>7018089</v>
+        <v>7018122</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838517</v>
+        <v>124838335</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1315,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609213</v>
+        <v>609210</v>
       </c>
       <c r="R8" t="n">
-        <v>7018077</v>
+        <v>7018126</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124834632</v>
+        <v>124835535</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1417,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609434</v>
+        <v>609344</v>
       </c>
       <c r="R9" t="n">
-        <v>7018063</v>
+        <v>7018135</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124835535</v>
+        <v>124834923</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>91673</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,25 +1515,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609344</v>
+        <v>609373</v>
       </c>
       <c r="R10" t="n">
-        <v>7018135</v>
+        <v>7018120</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,7 +1605,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124834715</v>
+        <v>124838495</v>
       </c>
       <c r="B11" t="n">
         <v>91299</v>
@@ -1637,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609370</v>
+        <v>609194</v>
       </c>
       <c r="R11" t="n">
-        <v>7018116</v>
+        <v>7018089</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124834309</v>
+        <v>124834632</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,42 +1719,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609474</v>
+        <v>609434</v>
       </c>
       <c r="R12" t="n">
-        <v>7018096</v>
+        <v>7018063</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1805,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124834208</v>
+        <v>124835238</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,25 +1821,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609480</v>
+        <v>609369</v>
       </c>
       <c r="R13" t="n">
-        <v>7018081</v>
+        <v>7018099</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838441</v>
+        <v>124838123</v>
       </c>
       <c r="B14" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,25 +1923,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609200</v>
+        <v>609231</v>
       </c>
       <c r="R14" t="n">
-        <v>7018089</v>
+        <v>7018145</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2009,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124834152</v>
+        <v>124838065</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2021,38 +2025,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609537</v>
+        <v>609237</v>
       </c>
       <c r="R15" t="n">
-        <v>7018055</v>
+        <v>7018136</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2111,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124834923</v>
+        <v>124834208</v>
       </c>
       <c r="B16" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,25 +2131,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2151,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609373</v>
+        <v>609480</v>
       </c>
       <c r="R16" t="n">
-        <v>7018120</v>
+        <v>7018081</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2213,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838613</v>
+        <v>124838441</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2229,38 +2237,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609220</v>
+        <v>609200</v>
       </c>
       <c r="R17" t="n">
-        <v>7018070</v>
+        <v>7018089</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2319,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838585</v>
+        <v>124838780</v>
       </c>
       <c r="B18" t="n">
-        <v>96985</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,38 +2335,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609220</v>
+        <v>609196</v>
       </c>
       <c r="R18" t="n">
-        <v>7018071</v>
+        <v>7018025</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2421,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124837877</v>
+        <v>124838585</v>
       </c>
       <c r="B19" t="n">
-        <v>91457</v>
+        <v>96985</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2433,25 +2442,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2461,10 +2470,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609243</v>
+        <v>609220</v>
       </c>
       <c r="R19" t="n">
-        <v>7018166</v>
+        <v>7018071</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2630,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838123</v>
+        <v>124838613</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2642,38 +2651,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609231</v>
+        <v>609220</v>
       </c>
       <c r="R21" t="n">
-        <v>7018145</v>
+        <v>7018070</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2732,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838262</v>
+        <v>124834715</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2744,42 +2757,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609214</v>
+        <v>609370</v>
       </c>
       <c r="R22" t="n">
-        <v>7018122</v>
+        <v>7018116</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2838,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838335</v>
+        <v>124837877</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2850,25 +2859,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2878,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609210</v>
+        <v>609243</v>
       </c>
       <c r="R23" t="n">
-        <v>7018126</v>
+        <v>7018166</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2940,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838065</v>
+        <v>124838321</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2952,42 +2961,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609237</v>
+        <v>609213</v>
       </c>
       <c r="R24" t="n">
-        <v>7018136</v>
+        <v>7018126</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3148,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838780</v>
+        <v>124838517</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,39 +3169,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609196</v>
+        <v>609213</v>
       </c>
       <c r="R26" t="n">
-        <v>7018025</v>
+        <v>7018077</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124835224</v>
+        <v>124838200</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609360</v>
+        <v>609219</v>
       </c>
       <c r="R4" t="n">
-        <v>7018113</v>
+        <v>7018134</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124838200</v>
+        <v>124835224</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609219</v>
+        <v>609360</v>
       </c>
       <c r="R5" t="n">
-        <v>7018134</v>
+        <v>7018113</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -1707,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124834632</v>
+        <v>124835238</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,25 +1719,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609434</v>
+        <v>609369</v>
       </c>
       <c r="R12" t="n">
-        <v>7018063</v>
+        <v>7018099</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124835238</v>
+        <v>124834632</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,25 +1821,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609369</v>
+        <v>609434</v>
       </c>
       <c r="R13" t="n">
-        <v>7018099</v>
+        <v>7018063</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124835280</v>
+        <v>124835224</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609347</v>
+        <v>609360</v>
       </c>
       <c r="R2" t="n">
-        <v>7018145</v>
+        <v>7018113</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124834152</v>
+        <v>124834632</v>
       </c>
       <c r="B3" t="n">
         <v>91299</v>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609537</v>
+        <v>609434</v>
       </c>
       <c r="R3" t="n">
-        <v>7018055</v>
+        <v>7018063</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124838200</v>
+        <v>124838780</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609219</v>
+        <v>609196</v>
       </c>
       <c r="R4" t="n">
-        <v>7018134</v>
+        <v>7018025</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124835224</v>
+        <v>124838441</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609360</v>
+        <v>609200</v>
       </c>
       <c r="R5" t="n">
-        <v>7018113</v>
+        <v>7018089</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124834267</v>
+        <v>124834923</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,38 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609474</v>
+        <v>609373</v>
       </c>
       <c r="R6" t="n">
-        <v>7018096</v>
+        <v>7018120</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838262</v>
+        <v>124838311</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,42 +1202,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609214</v>
+        <v>609215</v>
       </c>
       <c r="R7" t="n">
-        <v>7018122</v>
+        <v>7018125</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1299,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838335</v>
+        <v>124838585</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>96985</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609210</v>
+        <v>609220</v>
       </c>
       <c r="R8" t="n">
-        <v>7018126</v>
+        <v>7018071</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124835535</v>
+        <v>124837877</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609344</v>
+        <v>609243</v>
       </c>
       <c r="R9" t="n">
-        <v>7018135</v>
+        <v>7018166</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1503,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124834923</v>
+        <v>124838613</v>
       </c>
       <c r="B10" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,34 +1512,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609373</v>
+        <v>609220</v>
       </c>
       <c r="R10" t="n">
-        <v>7018120</v>
+        <v>7018070</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124838495</v>
+        <v>124835280</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,38 +1614,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609194</v>
+        <v>609347</v>
       </c>
       <c r="R11" t="n">
-        <v>7018089</v>
+        <v>7018145</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1707,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124835238</v>
+        <v>124838321</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,25 +1720,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609369</v>
+        <v>609213</v>
       </c>
       <c r="R12" t="n">
-        <v>7018099</v>
+        <v>7018126</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124834632</v>
+        <v>124834715</v>
       </c>
       <c r="B13" t="n">
         <v>91299</v>
@@ -1849,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609434</v>
+        <v>609370</v>
       </c>
       <c r="R13" t="n">
-        <v>7018063</v>
+        <v>7018116</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1911,7 +1912,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838123</v>
+        <v>124834208</v>
       </c>
       <c r="B14" t="n">
         <v>91012</v>
@@ -1951,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609231</v>
+        <v>609480</v>
       </c>
       <c r="R14" t="n">
-        <v>7018145</v>
+        <v>7018081</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2013,7 +2014,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838065</v>
+        <v>124838262</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2048,7 +2049,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2057,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609237</v>
+        <v>609214</v>
       </c>
       <c r="R15" t="n">
-        <v>7018136</v>
+        <v>7018122</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2119,7 +2120,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124834208</v>
+        <v>124838123</v>
       </c>
       <c r="B16" t="n">
         <v>91012</v>
@@ -2159,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609480</v>
+        <v>609231</v>
       </c>
       <c r="R16" t="n">
-        <v>7018081</v>
+        <v>7018145</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2221,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838441</v>
+        <v>124835238</v>
       </c>
       <c r="B17" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,25 +2234,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609200</v>
+        <v>609369</v>
       </c>
       <c r="R17" t="n">
-        <v>7018089</v>
+        <v>7018099</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2323,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838780</v>
+        <v>124834309</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,31 +2336,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609196</v>
+        <v>609474</v>
       </c>
       <c r="R18" t="n">
-        <v>7018025</v>
+        <v>7018096</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838585</v>
+        <v>124835535</v>
       </c>
       <c r="B19" t="n">
-        <v>96985</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2442,25 +2442,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609220</v>
+        <v>609344</v>
       </c>
       <c r="R19" t="n">
-        <v>7018071</v>
+        <v>7018135</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838613</v>
+        <v>124838335</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,42 +2651,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609220</v>
+        <v>609210</v>
       </c>
       <c r="R21" t="n">
-        <v>7018070</v>
+        <v>7018126</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2745,7 +2741,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124834715</v>
+        <v>124834152</v>
       </c>
       <c r="B22" t="n">
         <v>91299</v>
@@ -2785,10 +2781,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609370</v>
+        <v>609537</v>
       </c>
       <c r="R22" t="n">
-        <v>7018116</v>
+        <v>7018055</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2847,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124837877</v>
+        <v>124838517</v>
       </c>
       <c r="B23" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2859,25 +2855,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609243</v>
+        <v>609213</v>
       </c>
       <c r="R23" t="n">
-        <v>7018166</v>
+        <v>7018077</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2949,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838321</v>
+        <v>124838200</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2961,25 +2957,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2985,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609213</v>
+        <v>609219</v>
       </c>
       <c r="R24" t="n">
-        <v>7018126</v>
+        <v>7018134</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3051,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838311</v>
+        <v>124838065</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,38 +3059,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609215</v>
+        <v>609237</v>
       </c>
       <c r="R25" t="n">
-        <v>7018125</v>
+        <v>7018136</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838517</v>
+        <v>124838495</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609213</v>
+        <v>609194</v>
       </c>
       <c r="R26" t="n">
-        <v>7018077</v>
+        <v>7018089</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124835224</v>
+        <v>124838123</v>
       </c>
       <c r="B2" t="n">
         <v>91012</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609360</v>
+        <v>609231</v>
       </c>
       <c r="R2" t="n">
-        <v>7018113</v>
+        <v>7018145</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124834632</v>
+        <v>124838200</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609434</v>
+        <v>609219</v>
       </c>
       <c r="R3" t="n">
-        <v>7018063</v>
+        <v>7018134</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124838780</v>
+        <v>124834923</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>91673</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609196</v>
+        <v>609373</v>
       </c>
       <c r="R4" t="n">
-        <v>7018025</v>
+        <v>7018120</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124838441</v>
+        <v>124834309</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +997,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609200</v>
+        <v>609474</v>
       </c>
       <c r="R5" t="n">
-        <v>7018089</v>
+        <v>7018096</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124834923</v>
+        <v>124838262</v>
       </c>
       <c r="B6" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1103,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609373</v>
+        <v>609214</v>
       </c>
       <c r="R6" t="n">
-        <v>7018120</v>
+        <v>7018122</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1292,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838585</v>
+        <v>124834152</v>
       </c>
       <c r="B8" t="n">
-        <v>96985</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609220</v>
+        <v>609537</v>
       </c>
       <c r="R8" t="n">
-        <v>7018071</v>
+        <v>7018055</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124837877</v>
+        <v>124835238</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1409,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609243</v>
+        <v>609369</v>
       </c>
       <c r="R9" t="n">
-        <v>7018166</v>
+        <v>7018099</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,7 +1499,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124838613</v>
+        <v>124835280</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1531,7 +1534,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1540,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609220</v>
+        <v>609347</v>
       </c>
       <c r="R10" t="n">
-        <v>7018070</v>
+        <v>7018145</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124835280</v>
+        <v>124834208</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,42 +1617,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609347</v>
+        <v>609480</v>
       </c>
       <c r="R11" t="n">
-        <v>7018145</v>
+        <v>7018081</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838321</v>
+        <v>124834619</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,34 +1723,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609213</v>
+        <v>609432</v>
       </c>
       <c r="R12" t="n">
-        <v>7018126</v>
+        <v>7018063</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1912,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124834208</v>
+        <v>124838441</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,25 +1928,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609480</v>
+        <v>609200</v>
       </c>
       <c r="R14" t="n">
-        <v>7018081</v>
+        <v>7018089</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2014,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838262</v>
+        <v>124838321</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,42 +2030,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609214</v>
+        <v>609213</v>
       </c>
       <c r="R15" t="n">
-        <v>7018122</v>
+        <v>7018126</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838123</v>
+        <v>124838065</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,38 +2132,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609231</v>
+        <v>609237</v>
       </c>
       <c r="R16" t="n">
-        <v>7018145</v>
+        <v>7018136</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2222,10 +2226,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835238</v>
+        <v>124835224</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,25 +2238,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2266,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609369</v>
+        <v>609360</v>
       </c>
       <c r="R17" t="n">
-        <v>7018099</v>
+        <v>7018113</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2328,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124834309</v>
+        <v>124838335</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,42 +2340,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609474</v>
+        <v>609210</v>
       </c>
       <c r="R18" t="n">
-        <v>7018096</v>
+        <v>7018126</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124834619</v>
+        <v>124838517</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,39 +2548,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609432</v>
+        <v>609213</v>
       </c>
       <c r="R20" t="n">
-        <v>7018063</v>
+        <v>7018077</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2639,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838335</v>
+        <v>124838613</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,38 +2646,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609210</v>
+        <v>609220</v>
       </c>
       <c r="R21" t="n">
-        <v>7018126</v>
+        <v>7018070</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2741,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124834152</v>
+        <v>124838780</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,34 +2756,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609537</v>
+        <v>609196</v>
       </c>
       <c r="R22" t="n">
-        <v>7018055</v>
+        <v>7018025</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2843,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838517</v>
+        <v>124838495</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2859,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2883,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609213</v>
+        <v>609194</v>
       </c>
       <c r="R23" t="n">
-        <v>7018077</v>
+        <v>7018089</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838200</v>
+        <v>124837877</v>
       </c>
       <c r="B24" t="n">
-        <v>90977</v>
+        <v>91457</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2957,25 +2961,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2985,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609219</v>
+        <v>609243</v>
       </c>
       <c r="R24" t="n">
-        <v>7018134</v>
+        <v>7018166</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3047,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838065</v>
+        <v>124838585</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3059,42 +3063,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609237</v>
+        <v>609220</v>
       </c>
       <c r="R25" t="n">
-        <v>7018136</v>
+        <v>7018071</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838495</v>
+        <v>124834632</v>
       </c>
       <c r="B26" t="n">
         <v>91299</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609194</v>
+        <v>609434</v>
       </c>
       <c r="R26" t="n">
-        <v>7018089</v>
+        <v>7018063</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838311</v>
+        <v>124835238</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609215</v>
+        <v>609369</v>
       </c>
       <c r="R7" t="n">
-        <v>7018125</v>
+        <v>7018099</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124834152</v>
+        <v>124838311</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609537</v>
+        <v>609215</v>
       </c>
       <c r="R8" t="n">
-        <v>7018055</v>
+        <v>7018125</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124835238</v>
+        <v>124834152</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,25 +1409,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609369</v>
+        <v>609537</v>
       </c>
       <c r="R9" t="n">
-        <v>7018099</v>
+        <v>7018055</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838335</v>
+        <v>124838517</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609210</v>
+        <v>609213</v>
       </c>
       <c r="R18" t="n">
-        <v>7018126</v>
+        <v>7018077</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838517</v>
+        <v>124838335</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,21 +2548,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609213</v>
+        <v>609210</v>
       </c>
       <c r="R20" t="n">
-        <v>7018077</v>
+        <v>7018126</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124838123</v>
+        <v>124838495</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609231</v>
+        <v>609194</v>
       </c>
       <c r="R2" t="n">
-        <v>7018145</v>
+        <v>7018089</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838200</v>
+        <v>124838321</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609219</v>
+        <v>609213</v>
       </c>
       <c r="R3" t="n">
-        <v>7018134</v>
+        <v>7018126</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124834923</v>
+        <v>124838441</v>
       </c>
       <c r="B4" t="n">
-        <v>91673</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609373</v>
+        <v>609200</v>
       </c>
       <c r="R4" t="n">
-        <v>7018120</v>
+        <v>7018089</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124834309</v>
+        <v>124838517</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609474</v>
+        <v>609213</v>
       </c>
       <c r="R5" t="n">
-        <v>7018096</v>
+        <v>7018077</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124838262</v>
+        <v>124838335</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609214</v>
+        <v>609210</v>
       </c>
       <c r="R6" t="n">
-        <v>7018122</v>
+        <v>7018126</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124835238</v>
+        <v>124834309</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,38 +1197,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609369</v>
+        <v>609474</v>
       </c>
       <c r="R7" t="n">
-        <v>7018099</v>
+        <v>7018096</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838311</v>
+        <v>124838200</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609215</v>
+        <v>609219</v>
       </c>
       <c r="R8" t="n">
-        <v>7018125</v>
+        <v>7018134</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124834152</v>
+        <v>124838123</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609537</v>
+        <v>609231</v>
       </c>
       <c r="R9" t="n">
-        <v>7018055</v>
+        <v>7018145</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124835280</v>
+        <v>124834923</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,38 +1511,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609347</v>
+        <v>609373</v>
       </c>
       <c r="R10" t="n">
-        <v>7018145</v>
+        <v>7018120</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124834208</v>
+        <v>124834619</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,34 +1613,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609480</v>
+        <v>609432</v>
       </c>
       <c r="R11" t="n">
-        <v>7018081</v>
+        <v>7018063</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1707,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124834619</v>
+        <v>124835280</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,31 +1716,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1752,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609432</v>
+        <v>609347</v>
       </c>
       <c r="R12" t="n">
-        <v>7018063</v>
+        <v>7018145</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1814,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124834715</v>
+        <v>124838065</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,38 +1822,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609370</v>
+        <v>609237</v>
       </c>
       <c r="R13" t="n">
-        <v>7018116</v>
+        <v>7018136</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838441</v>
+        <v>124834208</v>
       </c>
       <c r="B14" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,25 +1928,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609200</v>
+        <v>609480</v>
       </c>
       <c r="R14" t="n">
-        <v>7018089</v>
+        <v>7018081</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,7 +2018,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838321</v>
+        <v>124835224</v>
       </c>
       <c r="B15" t="n">
         <v>91012</v>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609213</v>
+        <v>609360</v>
       </c>
       <c r="R15" t="n">
-        <v>7018126</v>
+        <v>7018113</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838065</v>
+        <v>124837877</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,38 +2136,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609237</v>
+        <v>609243</v>
       </c>
       <c r="R16" t="n">
-        <v>7018136</v>
+        <v>7018166</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2226,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835224</v>
+        <v>124835238</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2238,25 +2234,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2266,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609360</v>
+        <v>609369</v>
       </c>
       <c r="R17" t="n">
-        <v>7018113</v>
+        <v>7018099</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2328,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838517</v>
+        <v>124838311</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2340,25 +2336,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2368,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609213</v>
+        <v>609215</v>
       </c>
       <c r="R18" t="n">
-        <v>7018077</v>
+        <v>7018125</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2430,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124835535</v>
+        <v>124838585</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>96985</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2442,25 +2438,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2470,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609344</v>
+        <v>609220</v>
       </c>
       <c r="R19" t="n">
-        <v>7018135</v>
+        <v>7018071</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2532,7 +2528,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838335</v>
+        <v>124834152</v>
       </c>
       <c r="B20" t="n">
         <v>91299</v>
@@ -2572,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609210</v>
+        <v>609537</v>
       </c>
       <c r="R20" t="n">
-        <v>7018126</v>
+        <v>7018055</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2634,7 +2630,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838613</v>
+        <v>124838262</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2669,7 +2665,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2678,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609220</v>
+        <v>609214</v>
       </c>
       <c r="R21" t="n">
-        <v>7018070</v>
+        <v>7018122</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2740,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838780</v>
+        <v>124835535</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,39 +2752,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609196</v>
+        <v>609344</v>
       </c>
       <c r="R22" t="n">
-        <v>7018025</v>
+        <v>7018135</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2847,7 +2838,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838495</v>
+        <v>124834632</v>
       </c>
       <c r="B23" t="n">
         <v>91299</v>
@@ -2887,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609194</v>
+        <v>609434</v>
       </c>
       <c r="R23" t="n">
-        <v>7018089</v>
+        <v>7018063</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2949,10 +2940,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124837877</v>
+        <v>124838780</v>
       </c>
       <c r="B24" t="n">
-        <v>91457</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2961,38 +2952,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609243</v>
+        <v>609196</v>
       </c>
       <c r="R24" t="n">
-        <v>7018166</v>
+        <v>7018025</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3051,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838585</v>
+        <v>124838613</v>
       </c>
       <c r="B25" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,28 +3059,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
@@ -3094,7 +3094,7 @@
         <v>609220</v>
       </c>
       <c r="R25" t="n">
-        <v>7018071</v>
+        <v>7018070</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124834632</v>
+        <v>124834715</v>
       </c>
       <c r="B26" t="n">
         <v>91299</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609434</v>
+        <v>609370</v>
       </c>
       <c r="R26" t="n">
-        <v>7018063</v>
+        <v>7018116</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124838495</v>
+        <v>124834208</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609194</v>
+        <v>609480</v>
       </c>
       <c r="R2" t="n">
-        <v>7018089</v>
+        <v>7018081</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838321</v>
+        <v>124838585</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>96985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609213</v>
+        <v>609220</v>
       </c>
       <c r="R3" t="n">
-        <v>7018126</v>
+        <v>7018071</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124838441</v>
+        <v>124838517</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609200</v>
+        <v>609213</v>
       </c>
       <c r="R4" t="n">
-        <v>7018089</v>
+        <v>7018077</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124838517</v>
+        <v>124834632</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609213</v>
+        <v>609434</v>
       </c>
       <c r="R5" t="n">
-        <v>7018077</v>
+        <v>7018063</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124838335</v>
+        <v>124835238</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609210</v>
+        <v>609369</v>
       </c>
       <c r="R6" t="n">
-        <v>7018126</v>
+        <v>7018099</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124834309</v>
+        <v>124834267</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838200</v>
+        <v>124838613</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,38 +1303,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609219</v>
+        <v>609220</v>
       </c>
       <c r="R8" t="n">
-        <v>7018134</v>
+        <v>7018070</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838123</v>
+        <v>124838311</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,25 +1409,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609231</v>
+        <v>609215</v>
       </c>
       <c r="R9" t="n">
-        <v>7018145</v>
+        <v>7018125</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124834923</v>
+        <v>124838262</v>
       </c>
       <c r="B10" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,34 +1515,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609373</v>
+        <v>609214</v>
       </c>
       <c r="R10" t="n">
-        <v>7018120</v>
+        <v>7018122</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124834619</v>
+        <v>124834715</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,39 +1621,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609432</v>
+        <v>609370</v>
       </c>
       <c r="R11" t="n">
-        <v>7018063</v>
+        <v>7018116</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124835280</v>
+        <v>124837877</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,38 +1723,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609347</v>
+        <v>609243</v>
       </c>
       <c r="R12" t="n">
-        <v>7018145</v>
+        <v>7018166</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124838065</v>
+        <v>124838200</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,42 +1821,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609237</v>
+        <v>609219</v>
       </c>
       <c r="R13" t="n">
-        <v>7018136</v>
+        <v>7018134</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124834208</v>
+        <v>124838780</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,34 +1927,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609480</v>
+        <v>609196</v>
       </c>
       <c r="R14" t="n">
-        <v>7018081</v>
+        <v>7018025</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124835224</v>
+        <v>124838065</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,38 +2030,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609360</v>
+        <v>609237</v>
       </c>
       <c r="R15" t="n">
-        <v>7018113</v>
+        <v>7018136</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2120,10 +2124,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124837877</v>
+        <v>124835280</v>
       </c>
       <c r="B16" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,34 +2140,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609243</v>
+        <v>609347</v>
       </c>
       <c r="R16" t="n">
-        <v>7018166</v>
+        <v>7018145</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2222,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835238</v>
+        <v>124838495</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609369</v>
+        <v>609194</v>
       </c>
       <c r="R17" t="n">
-        <v>7018099</v>
+        <v>7018089</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838311</v>
+        <v>124834152</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609215</v>
+        <v>609537</v>
       </c>
       <c r="R18" t="n">
-        <v>7018125</v>
+        <v>7018055</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2426,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838585</v>
+        <v>124835224</v>
       </c>
       <c r="B19" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609220</v>
+        <v>609360</v>
       </c>
       <c r="R19" t="n">
-        <v>7018071</v>
+        <v>7018113</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2528,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124834152</v>
+        <v>124835535</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2544,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2568,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609537</v>
+        <v>609344</v>
       </c>
       <c r="R20" t="n">
-        <v>7018055</v>
+        <v>7018135</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2630,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838262</v>
+        <v>124834619</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2642,30 +2650,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2674,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609214</v>
+        <v>609432</v>
       </c>
       <c r="R21" t="n">
-        <v>7018122</v>
+        <v>7018063</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2736,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124835535</v>
+        <v>124838441</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,25 +2757,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2776,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609344</v>
+        <v>609200</v>
       </c>
       <c r="R22" t="n">
-        <v>7018135</v>
+        <v>7018089</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2838,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124834632</v>
+        <v>124838321</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2878,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609434</v>
+        <v>609213</v>
       </c>
       <c r="R23" t="n">
-        <v>7018063</v>
+        <v>7018126</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2940,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838780</v>
+        <v>124838335</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,39 +2965,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609196</v>
+        <v>609210</v>
       </c>
       <c r="R24" t="n">
-        <v>7018025</v>
+        <v>7018126</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3047,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838613</v>
+        <v>124834923</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,38 +3067,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609220</v>
+        <v>609373</v>
       </c>
       <c r="R25" t="n">
-        <v>7018070</v>
+        <v>7018120</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124834715</v>
+        <v>124838123</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609370</v>
+        <v>609231</v>
       </c>
       <c r="R26" t="n">
-        <v>7018116</v>
+        <v>7018145</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124834208</v>
+        <v>124838311</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609480</v>
+        <v>609215</v>
       </c>
       <c r="R2" t="n">
-        <v>7018081</v>
+        <v>7018125</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838585</v>
+        <v>124838321</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609220</v>
+        <v>609213</v>
       </c>
       <c r="R3" t="n">
-        <v>7018071</v>
+        <v>7018126</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124834632</v>
+        <v>124834309</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609434</v>
+        <v>609474</v>
       </c>
       <c r="R5" t="n">
-        <v>7018063</v>
+        <v>7018096</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124835238</v>
+        <v>124838613</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1099,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609369</v>
+        <v>609220</v>
       </c>
       <c r="R6" t="n">
-        <v>7018099</v>
+        <v>7018070</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124834267</v>
+        <v>124838495</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,42 +1205,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609474</v>
+        <v>609194</v>
       </c>
       <c r="R7" t="n">
-        <v>7018096</v>
+        <v>7018089</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838613</v>
+        <v>124838200</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,42 +1307,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609220</v>
+        <v>609219</v>
       </c>
       <c r="R8" t="n">
-        <v>7018070</v>
+        <v>7018134</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838311</v>
+        <v>124838123</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,25 +1409,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609215</v>
+        <v>609231</v>
       </c>
       <c r="R9" t="n">
-        <v>7018125</v>
+        <v>7018145</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124838262</v>
+        <v>124835224</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,42 +1511,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609214</v>
+        <v>609360</v>
       </c>
       <c r="R10" t="n">
-        <v>7018122</v>
+        <v>7018113</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124834715</v>
+        <v>124835238</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,25 +1613,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609370</v>
+        <v>609369</v>
       </c>
       <c r="R11" t="n">
-        <v>7018116</v>
+        <v>7018099</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1707,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124837877</v>
+        <v>124834208</v>
       </c>
       <c r="B12" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,25 +1715,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609243</v>
+        <v>609480</v>
       </c>
       <c r="R12" t="n">
-        <v>7018166</v>
+        <v>7018081</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124838200</v>
+        <v>124838780</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,38 +1817,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609219</v>
+        <v>609196</v>
       </c>
       <c r="R13" t="n">
-        <v>7018134</v>
+        <v>7018025</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1911,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838780</v>
+        <v>124838441</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>91457</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1923,43 +1924,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609196</v>
+        <v>609200</v>
       </c>
       <c r="R14" t="n">
-        <v>7018025</v>
+        <v>7018089</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838065</v>
+        <v>124838585</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,42 +2026,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609237</v>
+        <v>609220</v>
       </c>
       <c r="R15" t="n">
-        <v>7018136</v>
+        <v>7018071</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2124,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124835280</v>
+        <v>124834632</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,42 +2128,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609347</v>
+        <v>609434</v>
       </c>
       <c r="R16" t="n">
-        <v>7018145</v>
+        <v>7018063</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838495</v>
+        <v>124835535</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2234,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609194</v>
+        <v>609344</v>
       </c>
       <c r="R17" t="n">
-        <v>7018089</v>
+        <v>7018135</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,10 +2320,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124834152</v>
+        <v>124834619</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,34 +2336,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609537</v>
+        <v>609432</v>
       </c>
       <c r="R18" t="n">
-        <v>7018055</v>
+        <v>7018063</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124835224</v>
+        <v>124838065</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,38 +2439,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609360</v>
+        <v>609237</v>
       </c>
       <c r="R19" t="n">
-        <v>7018113</v>
+        <v>7018136</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2536,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124835535</v>
+        <v>124837877</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2545,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2573,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609344</v>
+        <v>609243</v>
       </c>
       <c r="R20" t="n">
-        <v>7018135</v>
+        <v>7018166</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2638,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124834619</v>
+        <v>124834923</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>91673</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,43 +2647,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609432</v>
+        <v>609373</v>
       </c>
       <c r="R21" t="n">
-        <v>7018063</v>
+        <v>7018120</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2745,10 +2737,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838441</v>
+        <v>124838335</v>
       </c>
       <c r="B22" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,25 +2749,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609200</v>
+        <v>609210</v>
       </c>
       <c r="R22" t="n">
-        <v>7018089</v>
+        <v>7018126</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2847,10 +2839,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838321</v>
+        <v>124838262</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2859,38 +2851,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609213</v>
+        <v>609214</v>
       </c>
       <c r="R23" t="n">
-        <v>7018126</v>
+        <v>7018122</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2949,7 +2945,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838335</v>
+        <v>124834152</v>
       </c>
       <c r="B24" t="n">
         <v>91299</v>
@@ -2989,10 +2985,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609210</v>
+        <v>609537</v>
       </c>
       <c r="R24" t="n">
-        <v>7018126</v>
+        <v>7018055</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3051,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124834923</v>
+        <v>124834715</v>
       </c>
       <c r="B25" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,25 +3059,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609373</v>
+        <v>609370</v>
       </c>
       <c r="R25" t="n">
-        <v>7018120</v>
+        <v>7018116</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838123</v>
+        <v>124835280</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,35 +3161,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609231</v>
+        <v>609347</v>
       </c>
       <c r="R26" t="n">
         <v>7018145</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124838311</v>
+        <v>124838321</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609215</v>
+        <v>609213</v>
       </c>
       <c r="R2" t="n">
-        <v>7018125</v>
+        <v>7018126</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838321</v>
+        <v>124838311</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609213</v>
+        <v>609215</v>
       </c>
       <c r="R3" t="n">
-        <v>7018126</v>
+        <v>7018125</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124838780</v>
+        <v>124838441</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>91457</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,43 +1817,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609196</v>
+        <v>609200</v>
       </c>
       <c r="R13" t="n">
-        <v>7018025</v>
+        <v>7018089</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838441</v>
+        <v>124838780</v>
       </c>
       <c r="B14" t="n">
-        <v>91457</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,38 +1919,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609200</v>
+        <v>609196</v>
       </c>
       <c r="R14" t="n">
-        <v>7018089</v>
+        <v>7018025</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835535</v>
+        <v>124834619</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,34 +2234,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609344</v>
+        <v>609432</v>
       </c>
       <c r="R17" t="n">
-        <v>7018135</v>
+        <v>7018063</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2320,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124834619</v>
+        <v>124835535</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,39 +2341,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609432</v>
+        <v>609344</v>
       </c>
       <c r="R18" t="n">
-        <v>7018063</v>
+        <v>7018135</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124838441</v>
+        <v>124838780</v>
       </c>
       <c r="B13" t="n">
-        <v>91457</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,38 +1817,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609200</v>
+        <v>609196</v>
       </c>
       <c r="R13" t="n">
-        <v>7018089</v>
+        <v>7018025</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838780</v>
+        <v>124838441</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>91457</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,43 +1924,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609196</v>
+        <v>609200</v>
       </c>
       <c r="R14" t="n">
-        <v>7018025</v>
+        <v>7018089</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124838321</v>
+        <v>124835535</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609213</v>
+        <v>609344</v>
       </c>
       <c r="R2" t="n">
-        <v>7018126</v>
+        <v>7018135</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838311</v>
+        <v>124835238</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609215</v>
+        <v>609369</v>
       </c>
       <c r="R3" t="n">
-        <v>7018125</v>
+        <v>7018099</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124838517</v>
+        <v>124834152</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609213</v>
+        <v>609537</v>
       </c>
       <c r="R4" t="n">
-        <v>7018077</v>
+        <v>7018055</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124834309</v>
+        <v>124837877</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609474</v>
+        <v>609243</v>
       </c>
       <c r="R5" t="n">
-        <v>7018096</v>
+        <v>7018166</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124838613</v>
+        <v>124834208</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609220</v>
+        <v>609480</v>
       </c>
       <c r="R6" t="n">
-        <v>7018070</v>
+        <v>7018081</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838495</v>
+        <v>124838311</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609194</v>
+        <v>609215</v>
       </c>
       <c r="R7" t="n">
-        <v>7018089</v>
+        <v>7018125</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838200</v>
+        <v>124834309</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,38 +1299,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609219</v>
+        <v>609474</v>
       </c>
       <c r="R8" t="n">
-        <v>7018134</v>
+        <v>7018096</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838123</v>
+        <v>124838441</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609231</v>
+        <v>609200</v>
       </c>
       <c r="R9" t="n">
-        <v>7018145</v>
+        <v>7018089</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124835224</v>
+        <v>124838200</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,25 +1507,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609360</v>
+        <v>609219</v>
       </c>
       <c r="R10" t="n">
-        <v>7018113</v>
+        <v>7018134</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124835238</v>
+        <v>124838585</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>96985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609369</v>
+        <v>609220</v>
       </c>
       <c r="R11" t="n">
-        <v>7018099</v>
+        <v>7018071</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1703,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124834208</v>
+        <v>124838613</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,38 +1711,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609480</v>
+        <v>609220</v>
       </c>
       <c r="R12" t="n">
-        <v>7018081</v>
+        <v>7018070</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124838780</v>
+        <v>124834923</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>91673</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,43 +1817,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609196</v>
+        <v>609373</v>
       </c>
       <c r="R13" t="n">
-        <v>7018025</v>
+        <v>7018120</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838441</v>
+        <v>124838517</v>
       </c>
       <c r="B14" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,25 +1919,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609200</v>
+        <v>609213</v>
       </c>
       <c r="R14" t="n">
-        <v>7018089</v>
+        <v>7018077</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2014,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838585</v>
+        <v>124838780</v>
       </c>
       <c r="B15" t="n">
-        <v>96985</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,38 +2021,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609220</v>
+        <v>609196</v>
       </c>
       <c r="R15" t="n">
-        <v>7018071</v>
+        <v>7018025</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124834632</v>
+        <v>124838123</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609434</v>
+        <v>609231</v>
       </c>
       <c r="R16" t="n">
-        <v>7018063</v>
+        <v>7018145</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124834619</v>
+        <v>124838262</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,31 +2230,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2263,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609432</v>
+        <v>609214</v>
       </c>
       <c r="R17" t="n">
-        <v>7018063</v>
+        <v>7018122</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2325,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124835535</v>
+        <v>124834619</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2341,34 +2340,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609344</v>
+        <v>609432</v>
       </c>
       <c r="R18" t="n">
-        <v>7018135</v>
+        <v>7018063</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2533,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124837877</v>
+        <v>124838335</v>
       </c>
       <c r="B20" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,25 +2549,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2573,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609243</v>
+        <v>609210</v>
       </c>
       <c r="R20" t="n">
-        <v>7018166</v>
+        <v>7018126</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2635,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124834923</v>
+        <v>124838495</v>
       </c>
       <c r="B21" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2647,25 +2651,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609373</v>
+        <v>609194</v>
       </c>
       <c r="R21" t="n">
-        <v>7018120</v>
+        <v>7018089</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2737,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838335</v>
+        <v>124835224</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2753,21 +2757,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2777,10 +2781,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609210</v>
+        <v>609360</v>
       </c>
       <c r="R22" t="n">
-        <v>7018126</v>
+        <v>7018113</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2839,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838262</v>
+        <v>124834715</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2851,42 +2855,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609214</v>
+        <v>609370</v>
       </c>
       <c r="R23" t="n">
-        <v>7018122</v>
+        <v>7018116</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124834152</v>
+        <v>124835280</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2957,38 +2957,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609537</v>
+        <v>609347</v>
       </c>
       <c r="R24" t="n">
-        <v>7018055</v>
+        <v>7018145</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3047,7 +3051,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124834715</v>
+        <v>124834632</v>
       </c>
       <c r="B25" t="n">
         <v>91299</v>
@@ -3087,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609370</v>
+        <v>609434</v>
       </c>
       <c r="R25" t="n">
-        <v>7018116</v>
+        <v>7018063</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3149,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124835280</v>
+        <v>124838321</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3161,42 +3165,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609347</v>
+        <v>609213</v>
       </c>
       <c r="R26" t="n">
-        <v>7018145</v>
+        <v>7018126</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124835535</v>
+        <v>124835238</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609344</v>
+        <v>609369</v>
       </c>
       <c r="R2" t="n">
-        <v>7018135</v>
+        <v>7018099</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124835238</v>
+        <v>124834923</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91673</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609369</v>
+        <v>609373</v>
       </c>
       <c r="R3" t="n">
-        <v>7018099</v>
+        <v>7018120</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124834152</v>
+        <v>124834208</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609537</v>
+        <v>609480</v>
       </c>
       <c r="R4" t="n">
-        <v>7018055</v>
+        <v>7018081</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124837877</v>
+        <v>124834619</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609243</v>
+        <v>609432</v>
       </c>
       <c r="R5" t="n">
-        <v>7018166</v>
+        <v>7018063</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124834208</v>
+        <v>124838200</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609480</v>
+        <v>609219</v>
       </c>
       <c r="R6" t="n">
-        <v>7018081</v>
+        <v>7018134</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1393,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838441</v>
+        <v>124838321</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609200</v>
+        <v>609213</v>
       </c>
       <c r="R9" t="n">
-        <v>7018089</v>
+        <v>7018126</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124838200</v>
+        <v>124838065</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,38 +1512,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609219</v>
+        <v>609237</v>
       </c>
       <c r="R10" t="n">
-        <v>7018134</v>
+        <v>7018136</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124838585</v>
+        <v>124838335</v>
       </c>
       <c r="B11" t="n">
-        <v>96985</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,25 +1618,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609220</v>
+        <v>609210</v>
       </c>
       <c r="R11" t="n">
-        <v>7018071</v>
+        <v>7018126</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838613</v>
+        <v>124834715</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,42 +1720,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609220</v>
+        <v>609370</v>
       </c>
       <c r="R12" t="n">
-        <v>7018070</v>
+        <v>7018116</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1805,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124834923</v>
+        <v>124838441</v>
       </c>
       <c r="B13" t="n">
-        <v>91673</v>
+        <v>91457</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609373</v>
+        <v>609200</v>
       </c>
       <c r="R13" t="n">
-        <v>7018120</v>
+        <v>7018089</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,7 +1912,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838517</v>
+        <v>124835224</v>
       </c>
       <c r="B14" t="n">
         <v>91012</v>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609213</v>
+        <v>609360</v>
       </c>
       <c r="R14" t="n">
-        <v>7018077</v>
+        <v>7018113</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2009,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838780</v>
+        <v>124838517</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,39 +2030,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609196</v>
+        <v>609213</v>
       </c>
       <c r="R15" t="n">
-        <v>7018025</v>
+        <v>7018077</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838123</v>
+        <v>124835535</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609231</v>
+        <v>609344</v>
       </c>
       <c r="R16" t="n">
-        <v>7018145</v>
+        <v>7018135</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838262</v>
+        <v>124835280</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609214</v>
+        <v>609347</v>
       </c>
       <c r="R17" t="n">
-        <v>7018122</v>
+        <v>7018145</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124834619</v>
+        <v>124838613</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,31 +2336,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2369,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609432</v>
+        <v>609220</v>
       </c>
       <c r="R18" t="n">
-        <v>7018063</v>
+        <v>7018070</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2431,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838065</v>
+        <v>124838123</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,42 +2442,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609237</v>
+        <v>609231</v>
       </c>
       <c r="R19" t="n">
-        <v>7018136</v>
+        <v>7018145</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2537,10 +2532,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838335</v>
+        <v>124838585</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>96985</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2549,25 +2544,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609210</v>
+        <v>609220</v>
       </c>
       <c r="R20" t="n">
-        <v>7018126</v>
+        <v>7018071</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2741,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124835224</v>
+        <v>124837877</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2753,25 +2748,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2781,10 +2776,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609360</v>
+        <v>609243</v>
       </c>
       <c r="R22" t="n">
-        <v>7018113</v>
+        <v>7018166</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2843,7 +2838,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124834715</v>
+        <v>124834152</v>
       </c>
       <c r="B23" t="n">
         <v>91299</v>
@@ -2883,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609370</v>
+        <v>609537</v>
       </c>
       <c r="R23" t="n">
-        <v>7018116</v>
+        <v>7018055</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,7 +2940,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124835280</v>
+        <v>124838262</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -2980,7 +2975,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2989,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609347</v>
+        <v>609214</v>
       </c>
       <c r="R24" t="n">
-        <v>7018145</v>
+        <v>7018122</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3153,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838321</v>
+        <v>124838780</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,34 +3164,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609213</v>
+        <v>609196</v>
       </c>
       <c r="R26" t="n">
-        <v>7018126</v>
+        <v>7018025</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124834923</v>
+        <v>124838262</v>
       </c>
       <c r="B3" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609373</v>
+        <v>609214</v>
       </c>
       <c r="R3" t="n">
-        <v>7018120</v>
+        <v>7018122</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124834208</v>
+        <v>124834309</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +895,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609480</v>
+        <v>609474</v>
       </c>
       <c r="R4" t="n">
-        <v>7018081</v>
+        <v>7018096</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124834619</v>
+        <v>124838613</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,31 +1001,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609432</v>
+        <v>609220</v>
       </c>
       <c r="R5" t="n">
-        <v>7018063</v>
+        <v>7018070</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124838200</v>
+        <v>124834152</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1107,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609219</v>
+        <v>609537</v>
       </c>
       <c r="R6" t="n">
-        <v>7018134</v>
+        <v>7018055</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838311</v>
+        <v>124838321</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1209,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609215</v>
+        <v>609213</v>
       </c>
       <c r="R7" t="n">
-        <v>7018125</v>
+        <v>7018126</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124834309</v>
+        <v>124838517</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,42 +1311,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609474</v>
+        <v>609213</v>
       </c>
       <c r="R8" t="n">
-        <v>7018096</v>
+        <v>7018077</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838321</v>
+        <v>124838495</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1417,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609213</v>
+        <v>609194</v>
       </c>
       <c r="R9" t="n">
-        <v>7018126</v>
+        <v>7018089</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124838065</v>
+        <v>124834632</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,42 +1515,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609237</v>
+        <v>609434</v>
       </c>
       <c r="R10" t="n">
-        <v>7018136</v>
+        <v>7018063</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124838335</v>
+        <v>124838065</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,38 +1617,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609210</v>
+        <v>609237</v>
       </c>
       <c r="R11" t="n">
-        <v>7018126</v>
+        <v>7018136</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124834715</v>
+        <v>124838585</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>96985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,25 +1723,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1748,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609370</v>
+        <v>609220</v>
       </c>
       <c r="R12" t="n">
-        <v>7018116</v>
+        <v>7018071</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124838441</v>
+        <v>124835280</v>
       </c>
       <c r="B13" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,34 +1829,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609200</v>
+        <v>609347</v>
       </c>
       <c r="R13" t="n">
-        <v>7018089</v>
+        <v>7018145</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2014,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838517</v>
+        <v>124838441</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609213</v>
+        <v>609200</v>
       </c>
       <c r="R15" t="n">
-        <v>7018077</v>
+        <v>7018089</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124835535</v>
+        <v>124837877</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609344</v>
+        <v>609243</v>
       </c>
       <c r="R16" t="n">
-        <v>7018135</v>
+        <v>7018166</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2218,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835280</v>
+        <v>124834715</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,42 +2237,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609347</v>
+        <v>609370</v>
       </c>
       <c r="R17" t="n">
-        <v>7018145</v>
+        <v>7018116</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838613</v>
+        <v>124835535</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,42 +2339,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609220</v>
+        <v>609344</v>
       </c>
       <c r="R18" t="n">
-        <v>7018070</v>
+        <v>7018135</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2430,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838123</v>
+        <v>124834208</v>
       </c>
       <c r="B19" t="n">
         <v>91012</v>
@@ -2470,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609231</v>
+        <v>609480</v>
       </c>
       <c r="R19" t="n">
-        <v>7018145</v>
+        <v>7018081</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2532,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838585</v>
+        <v>124834619</v>
       </c>
       <c r="B20" t="n">
-        <v>96985</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2544,38 +2543,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609220</v>
+        <v>609432</v>
       </c>
       <c r="R20" t="n">
-        <v>7018071</v>
+        <v>7018063</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2634,7 +2638,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838495</v>
+        <v>124838335</v>
       </c>
       <c r="B21" t="n">
         <v>91299</v>
@@ -2674,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609194</v>
+        <v>609210</v>
       </c>
       <c r="R21" t="n">
-        <v>7018089</v>
+        <v>7018126</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2736,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124837877</v>
+        <v>124838200</v>
       </c>
       <c r="B22" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2776,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609243</v>
+        <v>609219</v>
       </c>
       <c r="R22" t="n">
-        <v>7018166</v>
+        <v>7018134</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2838,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124834152</v>
+        <v>124834923</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2850,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2878,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609537</v>
+        <v>609373</v>
       </c>
       <c r="R23" t="n">
-        <v>7018055</v>
+        <v>7018120</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2940,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838262</v>
+        <v>124838311</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2952,42 +2956,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609214</v>
+        <v>609215</v>
       </c>
       <c r="R24" t="n">
-        <v>7018122</v>
+        <v>7018125</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124834632</v>
+        <v>124838123</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609434</v>
+        <v>609231</v>
       </c>
       <c r="R25" t="n">
-        <v>7018063</v>
+        <v>7018145</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -1813,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124835280</v>
+        <v>124835224</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,42 +1825,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609347</v>
+        <v>609360</v>
       </c>
       <c r="R13" t="n">
-        <v>7018145</v>
+        <v>7018113</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124835224</v>
+        <v>124838441</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1927,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609360</v>
+        <v>609200</v>
       </c>
       <c r="R14" t="n">
-        <v>7018113</v>
+        <v>7018089</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,7 +2017,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838441</v>
+        <v>124837877</v>
       </c>
       <c r="B15" t="n">
         <v>91457</v>
@@ -2061,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609200</v>
+        <v>609243</v>
       </c>
       <c r="R15" t="n">
-        <v>7018089</v>
+        <v>7018166</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124837877</v>
+        <v>124835280</v>
       </c>
       <c r="B16" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,34 +2135,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609243</v>
+        <v>609347</v>
       </c>
       <c r="R16" t="n">
-        <v>7018166</v>
+        <v>7018145</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838311</v>
+        <v>124838123</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609215</v>
+        <v>609231</v>
       </c>
       <c r="R24" t="n">
-        <v>7018125</v>
+        <v>7018145</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838123</v>
+        <v>124838311</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609231</v>
+        <v>609215</v>
       </c>
       <c r="R25" t="n">
-        <v>7018145</v>
+        <v>7018125</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124835238</v>
+        <v>124834619</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609369</v>
+        <v>609432</v>
       </c>
       <c r="R2" t="n">
-        <v>7018099</v>
+        <v>7018063</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838262</v>
+        <v>124835280</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -812,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609214</v>
+        <v>609347</v>
       </c>
       <c r="R3" t="n">
-        <v>7018122</v>
+        <v>7018145</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124834309</v>
+        <v>124835535</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609474</v>
+        <v>609344</v>
       </c>
       <c r="R4" t="n">
-        <v>7018096</v>
+        <v>7018135</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124838613</v>
+        <v>124838321</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,42 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609220</v>
+        <v>609213</v>
       </c>
       <c r="R5" t="n">
-        <v>7018070</v>
+        <v>7018126</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124834152</v>
+        <v>124834632</v>
       </c>
       <c r="B6" t="n">
         <v>91299</v>
@@ -1135,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609537</v>
+        <v>609434</v>
       </c>
       <c r="R6" t="n">
-        <v>7018055</v>
+        <v>7018063</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1197,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838321</v>
+        <v>124834208</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1237,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609213</v>
+        <v>609480</v>
       </c>
       <c r="R7" t="n">
-        <v>7018126</v>
+        <v>7018081</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1299,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838517</v>
+        <v>124838441</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609213</v>
+        <v>609200</v>
       </c>
       <c r="R8" t="n">
-        <v>7018077</v>
+        <v>7018089</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1503,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124834632</v>
+        <v>124834152</v>
       </c>
       <c r="B10" t="n">
         <v>91299</v>
@@ -1543,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609434</v>
+        <v>609537</v>
       </c>
       <c r="R10" t="n">
-        <v>7018063</v>
+        <v>7018055</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124838065</v>
+        <v>124837877</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,38 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609237</v>
+        <v>609243</v>
       </c>
       <c r="R11" t="n">
-        <v>7018136</v>
+        <v>7018166</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1711,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838585</v>
+        <v>124838065</v>
       </c>
       <c r="B12" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,38 +1716,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609220</v>
+        <v>609237</v>
       </c>
       <c r="R12" t="n">
-        <v>7018071</v>
+        <v>7018136</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1813,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124835224</v>
+        <v>124835238</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,25 +1822,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609360</v>
+        <v>609369</v>
       </c>
       <c r="R13" t="n">
-        <v>7018113</v>
+        <v>7018099</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1915,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838441</v>
+        <v>124838517</v>
       </c>
       <c r="B14" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,25 +1924,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609200</v>
+        <v>609213</v>
       </c>
       <c r="R14" t="n">
-        <v>7018089</v>
+        <v>7018077</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2017,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124837877</v>
+        <v>124838262</v>
       </c>
       <c r="B15" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,34 +2030,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609243</v>
+        <v>609214</v>
       </c>
       <c r="R15" t="n">
-        <v>7018166</v>
+        <v>7018122</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2119,7 +2120,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124835280</v>
+        <v>124838613</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2154,7 +2155,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2163,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609347</v>
+        <v>609220</v>
       </c>
       <c r="R16" t="n">
-        <v>7018145</v>
+        <v>7018070</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2226,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124834715</v>
+        <v>124838200</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2238,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2266,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609370</v>
+        <v>609219</v>
       </c>
       <c r="R17" t="n">
-        <v>7018116</v>
+        <v>7018134</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2327,10 +2328,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124835535</v>
+        <v>124838585</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>96985</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2340,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609344</v>
+        <v>609220</v>
       </c>
       <c r="R18" t="n">
-        <v>7018135</v>
+        <v>7018071</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124834208</v>
+        <v>124838335</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2446,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2470,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609480</v>
+        <v>609210</v>
       </c>
       <c r="R19" t="n">
-        <v>7018081</v>
+        <v>7018126</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2532,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124834619</v>
+        <v>124835224</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,39 +2548,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609432</v>
+        <v>609360</v>
       </c>
       <c r="R20" t="n">
-        <v>7018063</v>
+        <v>7018113</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2638,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838335</v>
+        <v>124834923</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2646,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609210</v>
+        <v>609373</v>
       </c>
       <c r="R21" t="n">
-        <v>7018126</v>
+        <v>7018120</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2740,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838200</v>
+        <v>124834267</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,38 +2748,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609219</v>
+        <v>609474</v>
       </c>
       <c r="R22" t="n">
-        <v>7018134</v>
+        <v>7018096</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124834923</v>
+        <v>124838123</v>
       </c>
       <c r="B23" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609373</v>
+        <v>609231</v>
       </c>
       <c r="R23" t="n">
-        <v>7018120</v>
+        <v>7018145</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838123</v>
+        <v>124838311</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609231</v>
+        <v>609215</v>
       </c>
       <c r="R24" t="n">
-        <v>7018145</v>
+        <v>7018125</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838311</v>
+        <v>124834715</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609215</v>
+        <v>609370</v>
       </c>
       <c r="R25" t="n">
-        <v>7018125</v>
+        <v>7018116</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124834619</v>
+        <v>124835535</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609432</v>
+        <v>609344</v>
       </c>
       <c r="R2" t="n">
-        <v>7018063</v>
+        <v>7018135</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124835280</v>
+        <v>124834619</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +789,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609347</v>
+        <v>609432</v>
       </c>
       <c r="R3" t="n">
-        <v>7018145</v>
+        <v>7018063</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124835535</v>
+        <v>124835280</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +896,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609344</v>
+        <v>609347</v>
       </c>
       <c r="R4" t="n">
-        <v>7018135</v>
+        <v>7018145</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124834715</v>
+        <v>124838780</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,34 +3062,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609370</v>
+        <v>609196</v>
       </c>
       <c r="R25" t="n">
-        <v>7018116</v>
+        <v>7018025</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3148,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838780</v>
+        <v>124834715</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,39 +3169,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609196</v>
+        <v>609370</v>
       </c>
       <c r="R26" t="n">
-        <v>7018025</v>
+        <v>7018116</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124835535</v>
+        <v>124834309</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609344</v>
+        <v>609474</v>
       </c>
       <c r="R2" t="n">
-        <v>7018135</v>
+        <v>7018096</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124834619</v>
+        <v>124834715</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609432</v>
+        <v>609370</v>
       </c>
       <c r="R3" t="n">
-        <v>7018063</v>
+        <v>7018116</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -990,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124838321</v>
+        <v>124834619</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,34 +1005,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609213</v>
+        <v>609432</v>
       </c>
       <c r="R5" t="n">
-        <v>7018126</v>
+        <v>7018063</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124834632</v>
+        <v>124835535</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609434</v>
+        <v>609344</v>
       </c>
       <c r="R6" t="n">
-        <v>7018063</v>
+        <v>7018135</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124834208</v>
+        <v>124838065</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,38 +1210,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609480</v>
+        <v>609237</v>
       </c>
       <c r="R7" t="n">
-        <v>7018081</v>
+        <v>7018136</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838441</v>
+        <v>124838321</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1316,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609200</v>
+        <v>609213</v>
       </c>
       <c r="R8" t="n">
-        <v>7018089</v>
+        <v>7018126</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838495</v>
+        <v>124838780</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,34 +1422,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609194</v>
+        <v>609196</v>
       </c>
       <c r="R9" t="n">
-        <v>7018089</v>
+        <v>7018025</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124834152</v>
+        <v>124837877</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609537</v>
+        <v>609243</v>
       </c>
       <c r="R10" t="n">
-        <v>7018055</v>
+        <v>7018166</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124837877</v>
+        <v>124835224</v>
       </c>
       <c r="B11" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1627,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609243</v>
+        <v>609360</v>
       </c>
       <c r="R11" t="n">
-        <v>7018166</v>
+        <v>7018113</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838065</v>
+        <v>124838441</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,38 +1733,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609237</v>
+        <v>609200</v>
       </c>
       <c r="R12" t="n">
-        <v>7018136</v>
+        <v>7018089</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124835238</v>
+        <v>124834152</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,25 +1831,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609369</v>
+        <v>609537</v>
       </c>
       <c r="R13" t="n">
-        <v>7018099</v>
+        <v>7018055</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838517</v>
+        <v>124838311</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,25 +1933,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1961,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609213</v>
+        <v>609215</v>
       </c>
       <c r="R14" t="n">
-        <v>7018077</v>
+        <v>7018125</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2014,10 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838262</v>
+        <v>124834632</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,42 +2035,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609214</v>
+        <v>609434</v>
       </c>
       <c r="R15" t="n">
-        <v>7018122</v>
+        <v>7018063</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2120,7 +2125,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838613</v>
+        <v>124838262</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2155,7 +2160,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2164,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609220</v>
+        <v>609214</v>
       </c>
       <c r="R16" t="n">
-        <v>7018070</v>
+        <v>7018122</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2226,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838200</v>
+        <v>124834208</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2238,25 +2243,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2266,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609219</v>
+        <v>609480</v>
       </c>
       <c r="R17" t="n">
-        <v>7018134</v>
+        <v>7018081</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2328,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838585</v>
+        <v>124838200</v>
       </c>
       <c r="B18" t="n">
-        <v>96985</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,21 +2349,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2368,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609220</v>
+        <v>609219</v>
       </c>
       <c r="R18" t="n">
-        <v>7018071</v>
+        <v>7018134</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2532,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124835224</v>
+        <v>124834923</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2544,25 +2549,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609360</v>
+        <v>609373</v>
       </c>
       <c r="R20" t="n">
-        <v>7018113</v>
+        <v>7018120</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2634,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124834923</v>
+        <v>124838613</v>
       </c>
       <c r="B21" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,34 +2655,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609373</v>
+        <v>609220</v>
       </c>
       <c r="R21" t="n">
-        <v>7018120</v>
+        <v>7018070</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2736,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124834267</v>
+        <v>124835238</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,42 +2757,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609474</v>
+        <v>609369</v>
       </c>
       <c r="R22" t="n">
-        <v>7018096</v>
+        <v>7018099</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2842,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838123</v>
+        <v>124838495</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609231</v>
+        <v>609194</v>
       </c>
       <c r="R23" t="n">
-        <v>7018145</v>
+        <v>7018089</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2944,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838311</v>
+        <v>124838123</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2961,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609215</v>
+        <v>609231</v>
       </c>
       <c r="R24" t="n">
-        <v>7018125</v>
+        <v>7018145</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3046,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838780</v>
+        <v>124838585</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>96985</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,43 +3063,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609196</v>
+        <v>609220</v>
       </c>
       <c r="R25" t="n">
-        <v>7018025</v>
+        <v>7018071</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124834715</v>
+        <v>124838517</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609370</v>
+        <v>609213</v>
       </c>
       <c r="R26" t="n">
-        <v>7018116</v>
+        <v>7018077</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124834309</v>
+        <v>124838613</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609474</v>
+        <v>609220</v>
       </c>
       <c r="R2" t="n">
-        <v>7018096</v>
+        <v>7018070</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124834715</v>
+        <v>124834152</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609370</v>
+        <v>609537</v>
       </c>
       <c r="R3" t="n">
-        <v>7018116</v>
+        <v>7018055</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124835280</v>
+        <v>124838585</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>97153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609347</v>
+        <v>609220</v>
       </c>
       <c r="R4" t="n">
-        <v>7018145</v>
+        <v>7018071</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124834619</v>
+        <v>124835280</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,31 +997,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1034,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609432</v>
+        <v>609347</v>
       </c>
       <c r="R5" t="n">
-        <v>7018063</v>
+        <v>7018145</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1096,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124835535</v>
+        <v>124837877</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>91617</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,25 +1103,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609344</v>
+        <v>609243</v>
       </c>
       <c r="R6" t="n">
-        <v>7018135</v>
+        <v>7018166</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1198,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838065</v>
+        <v>124834208</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,42 +1205,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609237</v>
+        <v>609480</v>
       </c>
       <c r="R7" t="n">
-        <v>7018136</v>
+        <v>7018081</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1304,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838321</v>
+        <v>124835238</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609213</v>
+        <v>609369</v>
       </c>
       <c r="R8" t="n">
-        <v>7018126</v>
+        <v>7018099</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1406,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838780</v>
+        <v>124838311</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>97147</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,43 +1409,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609196</v>
+        <v>609215</v>
       </c>
       <c r="R9" t="n">
-        <v>7018025</v>
+        <v>7018125</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1513,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124837877</v>
+        <v>124838200</v>
       </c>
       <c r="B10" t="n">
-        <v>91457</v>
+        <v>91131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609243</v>
+        <v>609219</v>
       </c>
       <c r="R10" t="n">
-        <v>7018166</v>
+        <v>7018134</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1615,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124835224</v>
+        <v>124834715</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609360</v>
+        <v>609370</v>
       </c>
       <c r="R11" t="n">
-        <v>7018113</v>
+        <v>7018116</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,7 +1706,7 @@
         <v>124838441</v>
       </c>
       <c r="B12" t="n">
-        <v>91457</v>
+        <v>91617</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124834152</v>
+        <v>124835224</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609537</v>
+        <v>609360</v>
       </c>
       <c r="R13" t="n">
-        <v>7018055</v>
+        <v>7018113</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1921,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838311</v>
+        <v>124834619</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>57632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,38 +1919,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609215</v>
+        <v>609432</v>
       </c>
       <c r="R14" t="n">
-        <v>7018125</v>
+        <v>7018063</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2023,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124834632</v>
+        <v>124835535</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>91184</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2039,21 +2030,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609434</v>
+        <v>609344</v>
       </c>
       <c r="R15" t="n">
-        <v>7018063</v>
+        <v>7018135</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2125,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838262</v>
+        <v>124838495</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,42 +2128,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609214</v>
+        <v>609194</v>
       </c>
       <c r="R16" t="n">
-        <v>7018122</v>
+        <v>7018089</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124834208</v>
+        <v>124834309</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2243,38 +2230,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609480</v>
+        <v>609474</v>
       </c>
       <c r="R17" t="n">
-        <v>7018081</v>
+        <v>7018096</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2333,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838200</v>
+        <v>124838321</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2345,25 +2336,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2373,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609219</v>
+        <v>609213</v>
       </c>
       <c r="R18" t="n">
-        <v>7018134</v>
+        <v>7018126</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2435,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838335</v>
+        <v>124834923</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>91833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,25 +2438,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609210</v>
+        <v>609373</v>
       </c>
       <c r="R19" t="n">
-        <v>7018126</v>
+        <v>7018120</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2537,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124834923</v>
+        <v>124838335</v>
       </c>
       <c r="B20" t="n">
-        <v>91673</v>
+        <v>91459</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2549,25 +2540,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609373</v>
+        <v>609210</v>
       </c>
       <c r="R20" t="n">
-        <v>7018120</v>
+        <v>7018126</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2639,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838613</v>
+        <v>124838780</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,30 +2642,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2683,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609220</v>
+        <v>609196</v>
       </c>
       <c r="R21" t="n">
-        <v>7018070</v>
+        <v>7018025</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2745,10 +2737,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124835238</v>
+        <v>124838065</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,38 +2749,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609369</v>
+        <v>609237</v>
       </c>
       <c r="R22" t="n">
-        <v>7018099</v>
+        <v>7018136</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2847,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838495</v>
+        <v>124838123</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2859,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609194</v>
+        <v>609231</v>
       </c>
       <c r="R23" t="n">
-        <v>7018089</v>
+        <v>7018145</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2949,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838123</v>
+        <v>124834632</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>91459</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,21 +2961,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2985,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609231</v>
+        <v>609434</v>
       </c>
       <c r="R24" t="n">
-        <v>7018145</v>
+        <v>7018063</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3051,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838585</v>
+        <v>124838262</v>
       </c>
       <c r="B25" t="n">
-        <v>96985</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,38 +3059,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609220</v>
+        <v>609214</v>
       </c>
       <c r="R25" t="n">
-        <v>7018071</v>
+        <v>7018122</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3156,7 +3156,7 @@
         <v>124838517</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>124835191</v>
       </c>
       <c r="B27" t="n">
-        <v>91705</v>
+        <v>91865</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124835535</v>
+        <v>124838495</v>
       </c>
       <c r="B15" t="n">
-        <v>91184</v>
+        <v>91459</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609344</v>
+        <v>609194</v>
       </c>
       <c r="R15" t="n">
-        <v>7018135</v>
+        <v>7018089</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838495</v>
+        <v>124835535</v>
       </c>
       <c r="B16" t="n">
-        <v>91459</v>
+        <v>91184</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609194</v>
+        <v>609344</v>
       </c>
       <c r="R16" t="n">
-        <v>7018089</v>
+        <v>7018135</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838780</v>
+        <v>124838065</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2642,31 +2642,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2675,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609196</v>
+        <v>609237</v>
       </c>
       <c r="R21" t="n">
-        <v>7018025</v>
+        <v>7018136</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2737,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838065</v>
+        <v>124838123</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,42 +2748,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609237</v>
+        <v>609231</v>
       </c>
       <c r="R22" t="n">
-        <v>7018136</v>
+        <v>7018145</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2843,10 +2838,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838123</v>
+        <v>124838780</v>
       </c>
       <c r="B23" t="n">
-        <v>91166</v>
+        <v>57632</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2859,34 +2854,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609231</v>
+        <v>609196</v>
       </c>
       <c r="R23" t="n">
-        <v>7018145</v>
+        <v>7018025</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838262</v>
+        <v>124838517</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3059,42 +3059,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609214</v>
+        <v>609213</v>
       </c>
       <c r="R25" t="n">
-        <v>7018122</v>
+        <v>7018077</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838517</v>
+        <v>124838262</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,38 +3161,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609213</v>
+        <v>609214</v>
       </c>
       <c r="R26" t="n">
-        <v>7018077</v>
+        <v>7018122</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124838613</v>
+        <v>124834632</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609220</v>
+        <v>609434</v>
       </c>
       <c r="R2" t="n">
-        <v>7018070</v>
+        <v>7018063</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124834152</v>
+        <v>124838065</v>
       </c>
       <c r="B3" t="n">
-        <v>91459</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609537</v>
+        <v>609237</v>
       </c>
       <c r="R3" t="n">
-        <v>7018055</v>
+        <v>7018136</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124838585</v>
+        <v>124834267</v>
       </c>
       <c r="B4" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +895,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609220</v>
+        <v>609474</v>
       </c>
       <c r="R4" t="n">
-        <v>7018071</v>
+        <v>7018096</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124835280</v>
+        <v>124838311</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>97147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1001,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609347</v>
+        <v>609215</v>
       </c>
       <c r="R5" t="n">
-        <v>7018145</v>
+        <v>7018125</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124837877</v>
+        <v>124835280</v>
       </c>
       <c r="B6" t="n">
-        <v>91617</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,34 +1107,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609243</v>
+        <v>609347</v>
       </c>
       <c r="R6" t="n">
-        <v>7018166</v>
+        <v>7018145</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124834208</v>
+        <v>124838441</v>
       </c>
       <c r="B7" t="n">
-        <v>91166</v>
+        <v>91617</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1209,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609480</v>
+        <v>609200</v>
       </c>
       <c r="R7" t="n">
-        <v>7018081</v>
+        <v>7018089</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124835238</v>
+        <v>124834715</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
+        <v>91459</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1311,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609369</v>
+        <v>609370</v>
       </c>
       <c r="R8" t="n">
-        <v>7018099</v>
+        <v>7018116</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838311</v>
+        <v>124834619</v>
       </c>
       <c r="B9" t="n">
-        <v>97147</v>
+        <v>57632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,38 +1413,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609215</v>
+        <v>609432</v>
       </c>
       <c r="R9" t="n">
-        <v>7018125</v>
+        <v>7018063</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124838200</v>
+        <v>124838613</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,38 +1520,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609219</v>
+        <v>609220</v>
       </c>
       <c r="R10" t="n">
-        <v>7018134</v>
+        <v>7018070</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124834715</v>
+        <v>124838123</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609370</v>
+        <v>609231</v>
       </c>
       <c r="R11" t="n">
-        <v>7018116</v>
+        <v>7018145</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1703,10 +1716,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838441</v>
+        <v>124838495</v>
       </c>
       <c r="B12" t="n">
-        <v>91617</v>
+        <v>91459</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,25 +1728,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,7 +1756,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609200</v>
+        <v>609194</v>
       </c>
       <c r="R12" t="n">
         <v>7018089</v>
@@ -1805,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124835224</v>
+        <v>124835238</v>
       </c>
       <c r="B13" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,25 +1830,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609360</v>
+        <v>609369</v>
       </c>
       <c r="R13" t="n">
-        <v>7018113</v>
+        <v>7018099</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124834619</v>
+        <v>124837877</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
+        <v>91617</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,43 +1932,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609432</v>
+        <v>609243</v>
       </c>
       <c r="R14" t="n">
-        <v>7018063</v>
+        <v>7018166</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2014,10 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838495</v>
+        <v>124838780</v>
       </c>
       <c r="B15" t="n">
-        <v>91459</v>
+        <v>57632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,34 +2038,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609194</v>
+        <v>609196</v>
       </c>
       <c r="R15" t="n">
-        <v>7018089</v>
+        <v>7018025</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124835535</v>
+        <v>124838517</v>
       </c>
       <c r="B16" t="n">
-        <v>91184</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2145,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609344</v>
+        <v>609213</v>
       </c>
       <c r="R16" t="n">
-        <v>7018135</v>
+        <v>7018077</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2218,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124834309</v>
+        <v>124835224</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,42 +2243,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609474</v>
+        <v>609360</v>
       </c>
       <c r="R17" t="n">
-        <v>7018096</v>
+        <v>7018113</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838321</v>
+        <v>124838585</v>
       </c>
       <c r="B18" t="n">
-        <v>91166</v>
+        <v>97153</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,25 +2345,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609213</v>
+        <v>609220</v>
       </c>
       <c r="R18" t="n">
-        <v>7018126</v>
+        <v>7018071</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2426,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124834923</v>
+        <v>124838200</v>
       </c>
       <c r="B19" t="n">
-        <v>91833</v>
+        <v>91131</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,25 +2447,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609373</v>
+        <v>609219</v>
       </c>
       <c r="R19" t="n">
-        <v>7018120</v>
+        <v>7018134</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2528,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838335</v>
+        <v>124834208</v>
       </c>
       <c r="B20" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2544,21 +2553,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2568,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609210</v>
+        <v>609480</v>
       </c>
       <c r="R20" t="n">
-        <v>7018126</v>
+        <v>7018081</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2630,7 +2639,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838065</v>
+        <v>124838262</v>
       </c>
       <c r="B21" t="n">
         <v>98269</v>
@@ -2665,7 +2674,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2674,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609237</v>
+        <v>609214</v>
       </c>
       <c r="R21" t="n">
-        <v>7018136</v>
+        <v>7018122</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2736,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838123</v>
+        <v>124834923</v>
       </c>
       <c r="B22" t="n">
-        <v>91166</v>
+        <v>91833</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,25 +2757,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2776,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609231</v>
+        <v>609373</v>
       </c>
       <c r="R22" t="n">
-        <v>7018145</v>
+        <v>7018120</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2838,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838780</v>
+        <v>124835535</v>
       </c>
       <c r="B23" t="n">
-        <v>57632</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,39 +2863,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609196</v>
+        <v>609344</v>
       </c>
       <c r="R23" t="n">
-        <v>7018025</v>
+        <v>7018135</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124834632</v>
+        <v>124838321</v>
       </c>
       <c r="B24" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2961,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2985,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609434</v>
+        <v>609213</v>
       </c>
       <c r="R24" t="n">
-        <v>7018063</v>
+        <v>7018126</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3047,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838517</v>
+        <v>124834152</v>
       </c>
       <c r="B25" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609213</v>
+        <v>609537</v>
       </c>
       <c r="R25" t="n">
-        <v>7018077</v>
+        <v>7018055</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3149,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838262</v>
+        <v>124838335</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3161,42 +3165,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609214</v>
+        <v>609210</v>
       </c>
       <c r="R26" t="n">
-        <v>7018122</v>
+        <v>7018126</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -2333,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838585</v>
+        <v>124838200</v>
       </c>
       <c r="B18" t="n">
-        <v>97153</v>
+        <v>91131</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609220</v>
+        <v>609219</v>
       </c>
       <c r="R18" t="n">
-        <v>7018071</v>
+        <v>7018134</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838200</v>
+        <v>124834208</v>
       </c>
       <c r="B19" t="n">
-        <v>91131</v>
+        <v>91166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,25 +2447,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609219</v>
+        <v>609480</v>
       </c>
       <c r="R19" t="n">
-        <v>7018134</v>
+        <v>7018081</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124834208</v>
+        <v>124838585</v>
       </c>
       <c r="B20" t="n">
-        <v>91166</v>
+        <v>97153</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2549,25 +2549,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609480</v>
+        <v>609220</v>
       </c>
       <c r="R20" t="n">
-        <v>7018081</v>
+        <v>7018071</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124834632</v>
+        <v>124838200</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609434</v>
+        <v>609219</v>
       </c>
       <c r="R2" t="n">
-        <v>7018063</v>
+        <v>7018134</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124838065</v>
+        <v>124838321</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609237</v>
+        <v>609213</v>
       </c>
       <c r="R3" t="n">
-        <v>7018136</v>
+        <v>7018126</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124834267</v>
+        <v>124834715</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609474</v>
+        <v>609370</v>
       </c>
       <c r="R4" t="n">
-        <v>7018096</v>
+        <v>7018116</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,50 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124838311</v>
+        <v>124838613</v>
       </c>
       <c r="B5" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609215</v>
+        <v>609220</v>
       </c>
       <c r="R5" t="n">
-        <v>7018125</v>
+        <v>7018070</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,54 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124835280</v>
+        <v>124838335</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609347</v>
+        <v>609210</v>
       </c>
       <c r="R6" t="n">
-        <v>7018145</v>
+        <v>7018126</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1197,37 +1164,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124838441</v>
+        <v>124838311</v>
       </c>
       <c r="B7" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609200</v>
+        <v>609215</v>
       </c>
       <c r="R7" t="n">
-        <v>7018089</v>
+        <v>7018125</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1299,16 +1261,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124834715</v>
+        <v>124834152</v>
       </c>
       <c r="B8" t="n">
         <v>91459</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1339,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609370</v>
+        <v>609537</v>
       </c>
       <c r="R8" t="n">
-        <v>7018116</v>
+        <v>7018055</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,15 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124834619</v>
+        <v>124835224</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,39 +1369,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609432</v>
+        <v>609360</v>
       </c>
       <c r="R9" t="n">
-        <v>7018063</v>
+        <v>7018113</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1508,54 +1455,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124838613</v>
+        <v>124834632</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609220</v>
+        <v>609434</v>
       </c>
       <c r="R10" t="n">
-        <v>7018070</v>
+        <v>7018063</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1614,37 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124838123</v>
+        <v>124838585</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609231</v>
+        <v>609220</v>
       </c>
       <c r="R11" t="n">
-        <v>7018145</v>
+        <v>7018071</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1716,15 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838495</v>
+        <v>124834619</v>
       </c>
       <c r="B12" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,34 +1660,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609194</v>
+        <v>609432</v>
       </c>
       <c r="R12" t="n">
-        <v>7018089</v>
+        <v>7018063</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1818,37 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124835238</v>
+        <v>124835535</v>
       </c>
       <c r="B13" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609369</v>
+        <v>609344</v>
       </c>
       <c r="R13" t="n">
-        <v>7018099</v>
+        <v>7018135</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1920,15 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124837877</v>
+        <v>124838262</v>
       </c>
       <c r="B14" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,34 +1859,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609243</v>
+        <v>609214</v>
       </c>
       <c r="R14" t="n">
-        <v>7018166</v>
+        <v>7018122</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2022,55 +1949,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838780</v>
+        <v>124837877</v>
       </c>
       <c r="B15" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609196</v>
+        <v>609243</v>
       </c>
       <c r="R15" t="n">
-        <v>7018025</v>
+        <v>7018166</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2129,16 +2046,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838517</v>
+        <v>124834208</v>
       </c>
       <c r="B16" t="n">
         <v>91166</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2169,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609213</v>
+        <v>609480</v>
       </c>
       <c r="R16" t="n">
-        <v>7018077</v>
+        <v>7018081</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2231,15 +2143,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835224</v>
+        <v>124838495</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,21 +2154,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2271,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609360</v>
+        <v>609194</v>
       </c>
       <c r="R17" t="n">
-        <v>7018113</v>
+        <v>7018089</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2333,50 +2240,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838200</v>
+        <v>124835280</v>
       </c>
       <c r="B18" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609219</v>
+        <v>609347</v>
       </c>
       <c r="R18" t="n">
-        <v>7018134</v>
+        <v>7018145</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2435,50 +2341,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124834208</v>
+        <v>124834309</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609480</v>
+        <v>609474</v>
       </c>
       <c r="R19" t="n">
-        <v>7018081</v>
+        <v>7018096</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2537,37 +2442,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838585</v>
+        <v>124838441</v>
       </c>
       <c r="B20" t="n">
-        <v>97153</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91617</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609220</v>
+        <v>609200</v>
       </c>
       <c r="R20" t="n">
-        <v>7018071</v>
+        <v>7018089</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2639,54 +2539,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838262</v>
+        <v>124838517</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609214</v>
+        <v>609213</v>
       </c>
       <c r="R21" t="n">
-        <v>7018122</v>
+        <v>7018077</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2745,37 +2636,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124834923</v>
+        <v>124838123</v>
       </c>
       <c r="B22" t="n">
-        <v>91833</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609373</v>
+        <v>609231</v>
       </c>
       <c r="R22" t="n">
-        <v>7018120</v>
+        <v>7018145</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2847,37 +2733,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124835535</v>
+        <v>124834923</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609344</v>
+        <v>609373</v>
       </c>
       <c r="R23" t="n">
-        <v>7018135</v>
+        <v>7018120</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2949,15 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838321</v>
+        <v>124838780</v>
       </c>
       <c r="B24" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,34 +2841,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609213</v>
+        <v>609196</v>
       </c>
       <c r="R24" t="n">
-        <v>7018126</v>
+        <v>7018025</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3051,37 +2932,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124834152</v>
+        <v>124835238</v>
       </c>
       <c r="B25" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +2967,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609537</v>
+        <v>609369</v>
       </c>
       <c r="R25" t="n">
-        <v>7018055</v>
+        <v>7018099</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3153,50 +3029,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838335</v>
+        <v>124838065</v>
       </c>
       <c r="B26" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609210</v>
+        <v>609237</v>
       </c>
       <c r="R26" t="n">
-        <v>7018126</v>
+        <v>7018136</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3259,11 +3134,6 @@
       </c>
       <c r="B27" t="n">
         <v>91865</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,980 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126095309</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>658</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>609501</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7018108</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126093304</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>609544</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7018077</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126093824</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>609306</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7018164</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126093862</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>609311</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7018162</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126093400</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>658</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>609453</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7018106</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126093369</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>609461</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7018120</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126093615</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>658</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>609363</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7018109</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126093939</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>609311</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7018163</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126093453</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>658</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>609432</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7018070</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126093372</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>609467</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7018145</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3234,7 +3234,7 @@
         <v>126095309</v>
       </c>
       <c r="B28" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126093304</v>
+        <v>126093824</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609544</v>
+        <v>609306</v>
       </c>
       <c r="R29" t="n">
-        <v>7018077</v>
+        <v>7018164</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126093824</v>
+        <v>126093304</v>
       </c>
       <c r="B30" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609306</v>
+        <v>609544</v>
       </c>
       <c r="R30" t="n">
-        <v>7018164</v>
+        <v>7018077</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>126093862</v>
       </c>
       <c r="B31" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>126093400</v>
       </c>
       <c r="B32" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>126093369</v>
       </c>
       <c r="B33" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>126093615</v>
       </c>
       <c r="B34" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126093939</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>126093453</v>
       </c>
       <c r="B36" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126093372</v>
       </c>
       <c r="B37" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3234,7 +3234,7 @@
         <v>126095309</v>
       </c>
       <c r="B28" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126093824</v>
+        <v>126093304</v>
       </c>
       <c r="B29" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609306</v>
+        <v>609544</v>
       </c>
       <c r="R29" t="n">
-        <v>7018164</v>
+        <v>7018077</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126093304</v>
+        <v>126093824</v>
       </c>
       <c r="B30" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609544</v>
+        <v>609306</v>
       </c>
       <c r="R30" t="n">
-        <v>7018077</v>
+        <v>7018164</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>126093400</v>
       </c>
       <c r="B32" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>126093369</v>
       </c>
       <c r="B33" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>126093615</v>
       </c>
       <c r="B34" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126093939</v>
       </c>
       <c r="B35" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>126093453</v>
       </c>
       <c r="B36" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126093372</v>
       </c>
       <c r="B37" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3234,7 +3234,7 @@
         <v>126095309</v>
       </c>
       <c r="B28" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>126093304</v>
       </c>
       <c r="B29" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>126093824</v>
       </c>
       <c r="B30" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>126093400</v>
       </c>
       <c r="B32" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>126093369</v>
       </c>
       <c r="B33" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>126093615</v>
       </c>
       <c r="B34" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126093939</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>126093453</v>
       </c>
       <c r="B36" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126093372</v>
       </c>
       <c r="B37" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3234,7 +3234,7 @@
         <v>126095309</v>
       </c>
       <c r="B28" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>126093304</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>126093824</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>126093862</v>
       </c>
       <c r="B31" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>126093400</v>
       </c>
       <c r="B32" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>126093369</v>
       </c>
       <c r="B33" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>126093615</v>
       </c>
       <c r="B34" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126093939</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>126093453</v>
       </c>
       <c r="B36" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126093372</v>
       </c>
       <c r="B37" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3331,7 +3331,7 @@
         <v>126093304</v>
       </c>
       <c r="B29" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>126093824</v>
       </c>
       <c r="B30" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126093939</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3234,7 +3234,7 @@
         <v>126095309</v>
       </c>
       <c r="B28" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>126093304</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>126093824</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>126093862</v>
       </c>
       <c r="B31" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>126093400</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>126093369</v>
       </c>
       <c r="B33" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>126093615</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126093939</v>
       </c>
       <c r="B35" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>126093453</v>
       </c>
       <c r="B36" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126093372</v>
       </c>
       <c r="B37" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3328,7 +3328,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126093304</v>
+        <v>126093824</v>
       </c>
       <c r="B29" t="n">
         <v>98361</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609544</v>
+        <v>609306</v>
       </c>
       <c r="R29" t="n">
-        <v>7018077</v>
+        <v>7018164</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126093824</v>
+        <v>126093304</v>
       </c>
       <c r="B30" t="n">
         <v>98361</v>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609306</v>
+        <v>609544</v>
       </c>
       <c r="R30" t="n">
-        <v>7018164</v>
+        <v>7018077</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -3328,7 +3328,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126093824</v>
+        <v>126093304</v>
       </c>
       <c r="B29" t="n">
         <v>98361</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609306</v>
+        <v>609544</v>
       </c>
       <c r="R29" t="n">
-        <v>7018164</v>
+        <v>7018077</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126093304</v>
+        <v>126093824</v>
       </c>
       <c r="B30" t="n">
         <v>98361</v>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609544</v>
+        <v>609306</v>
       </c>
       <c r="R30" t="n">
-        <v>7018077</v>
+        <v>7018164</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -4205,10 +4205,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127025224</v>
+        <v>127025234</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4244,13 +4244,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609220</v>
+        <v>609464</v>
       </c>
       <c r="R38" t="n">
-        <v>7018063</v>
+        <v>7018085</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4316,10 +4316,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127025234</v>
+        <v>127025224</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609464</v>
+        <v>609220</v>
       </c>
       <c r="R39" t="n">
-        <v>7018085</v>
+        <v>7018063</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4430,7 +4430,7 @@
         <v>127025225</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4538,10 +4538,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127025233</v>
+        <v>127025209</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4577,13 +4577,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>609445</v>
+        <v>609319</v>
       </c>
       <c r="R41" t="n">
-        <v>7018098</v>
+        <v>7018124</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127025209</v>
+        <v>127025233</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4688,13 +4688,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>609319</v>
+        <v>609445</v>
       </c>
       <c r="R42" t="n">
-        <v>7018124</v>
+        <v>7018098</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4763,7 +4763,7 @@
         <v>127025218</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>127025226</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127025231</v>
+        <v>127025227</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609305</v>
+        <v>609242</v>
       </c>
       <c r="R45" t="n">
-        <v>7018111</v>
+        <v>7018088</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5093,10 +5093,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127025227</v>
+        <v>127025231</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609242</v>
+        <v>609305</v>
       </c>
       <c r="R46" t="n">
-        <v>7018088</v>
+        <v>7018111</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5207,7 +5207,7 @@
         <v>127025221</v>
       </c>
       <c r="B47" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>127025214</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025230</v>
+        <v>127025236</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609292</v>
+        <v>609519</v>
       </c>
       <c r="R49" t="n">
-        <v>7018117</v>
+        <v>7018075</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5542,10 +5542,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025236</v>
+        <v>127025230</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5581,13 +5581,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609519</v>
+        <v>609292</v>
       </c>
       <c r="R50" t="n">
-        <v>7018075</v>
+        <v>7018117</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5653,10 +5653,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025210</v>
+        <v>127025211</v>
       </c>
       <c r="B51" t="n">
-        <v>91541</v>
+        <v>91319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5664,21 +5664,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609310</v>
+        <v>609316</v>
       </c>
       <c r="R51" t="n">
-        <v>7018130</v>
+        <v>7018135</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5764,10 +5764,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127025211</v>
+        <v>127025210</v>
       </c>
       <c r="B52" t="n">
-        <v>91245</v>
+        <v>91615</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609316</v>
+        <v>609310</v>
       </c>
       <c r="R52" t="n">
-        <v>7018135</v>
+        <v>7018130</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5878,7 +5878,7 @@
         <v>127025229</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5986,10 +5986,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127025228</v>
+        <v>127025222</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609266</v>
+        <v>609232</v>
       </c>
       <c r="R54" t="n">
-        <v>7018108</v>
+        <v>7018046</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,10 +6097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127025222</v>
+        <v>127025228</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609232</v>
+        <v>609266</v>
       </c>
       <c r="R55" t="n">
-        <v>7018046</v>
+        <v>7018108</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6208,10 +6208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127025215</v>
+        <v>127025219</v>
       </c>
       <c r="B56" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609274</v>
+        <v>609177</v>
       </c>
       <c r="R56" t="n">
-        <v>7018130</v>
+        <v>7018075</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6292,7 +6292,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6319,10 +6324,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127025219</v>
+        <v>127025215</v>
       </c>
       <c r="B57" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6349,7 +6354,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6358,10 +6363,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609177</v>
+        <v>609274</v>
       </c>
       <c r="R57" t="n">
-        <v>7018075</v>
+        <v>7018130</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6393,7 +6398,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6403,12 +6408,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6438,7 +6438,7 @@
         <v>127025238</v>
       </c>
       <c r="B58" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>127025212</v>
       </c>
       <c r="B59" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>127025216</v>
       </c>
       <c r="B60" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127025213</v>
+        <v>127025217</v>
       </c>
       <c r="B61" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6807,13 +6807,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609304</v>
+        <v>609201</v>
       </c>
       <c r="R61" t="n">
-        <v>7018131</v>
+        <v>7018130</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6879,10 +6879,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127025217</v>
+        <v>127025213</v>
       </c>
       <c r="B62" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6918,13 +6918,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609201</v>
+        <v>609304</v>
       </c>
       <c r="R62" t="n">
-        <v>7018130</v>
+        <v>7018131</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6993,7 +6993,7 @@
         <v>127025232</v>
       </c>
       <c r="B63" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>127025235</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -4208,7 +4208,7 @@
         <v>127025234</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>127025224</v>
       </c>
       <c r="B39" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>127025225</v>
       </c>
       <c r="B40" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>127025209</v>
       </c>
       <c r="B41" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127025233</v>
       </c>
       <c r="B42" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>127025218</v>
       </c>
       <c r="B43" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>127025226</v>
       </c>
       <c r="B44" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127025227</v>
+        <v>127025231</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609242</v>
+        <v>609305</v>
       </c>
       <c r="R45" t="n">
-        <v>7018088</v>
+        <v>7018111</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5093,10 +5093,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127025231</v>
+        <v>127025227</v>
       </c>
       <c r="B46" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609305</v>
+        <v>609242</v>
       </c>
       <c r="R46" t="n">
-        <v>7018111</v>
+        <v>7018088</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5207,7 +5207,7 @@
         <v>127025221</v>
       </c>
       <c r="B47" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>127025214</v>
       </c>
       <c r="B48" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025236</v>
+        <v>127025230</v>
       </c>
       <c r="B49" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609519</v>
+        <v>609292</v>
       </c>
       <c r="R49" t="n">
-        <v>7018075</v>
+        <v>7018117</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5542,10 +5542,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025230</v>
+        <v>127025236</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5581,13 +5581,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609292</v>
+        <v>609519</v>
       </c>
       <c r="R50" t="n">
-        <v>7018117</v>
+        <v>7018075</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5653,37 +5653,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025211</v>
+        <v>127025229</v>
       </c>
       <c r="B51" t="n">
-        <v>91319</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609316</v>
+        <v>609265</v>
       </c>
       <c r="R51" t="n">
-        <v>7018135</v>
+        <v>7018132</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5767,7 +5767,7 @@
         <v>127025210</v>
       </c>
       <c r="B52" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5875,37 +5875,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127025229</v>
+        <v>127025211</v>
       </c>
       <c r="B53" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609265</v>
+        <v>609316</v>
       </c>
       <c r="R53" t="n">
-        <v>7018132</v>
+        <v>7018135</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5989,7 +5989,7 @@
         <v>127025222</v>
       </c>
       <c r="B54" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>127025228</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>127025219</v>
       </c>
       <c r="B56" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>127025215</v>
       </c>
       <c r="B57" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127025238</v>
+        <v>127025212</v>
       </c>
       <c r="B58" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609526</v>
+        <v>609307</v>
       </c>
       <c r="R58" t="n">
-        <v>7018059</v>
+        <v>7018143</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6546,10 +6546,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127025212</v>
+        <v>127025238</v>
       </c>
       <c r="B59" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609307</v>
+        <v>609526</v>
       </c>
       <c r="R59" t="n">
-        <v>7018143</v>
+        <v>7018059</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6660,7 +6660,7 @@
         <v>127025216</v>
       </c>
       <c r="B60" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127025217</v>
+        <v>127025232</v>
       </c>
       <c r="B61" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609201</v>
+        <v>609323</v>
       </c>
       <c r="R61" t="n">
-        <v>7018130</v>
+        <v>7018111</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6879,10 +6879,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127025213</v>
+        <v>127025217</v>
       </c>
       <c r="B62" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6918,13 +6918,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609304</v>
+        <v>609201</v>
       </c>
       <c r="R62" t="n">
-        <v>7018131</v>
+        <v>7018130</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6990,10 +6990,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127025232</v>
+        <v>127025213</v>
       </c>
       <c r="B63" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7029,13 +7029,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609323</v>
+        <v>609304</v>
       </c>
       <c r="R63" t="n">
-        <v>7018111</v>
+        <v>7018131</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7104,7 +7104,7 @@
         <v>127025235</v>
       </c>
       <c r="B64" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -4982,7 +4982,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127025231</v>
+        <v>127025227</v>
       </c>
       <c r="B45" t="n">
         <v>98442</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609305</v>
+        <v>609242</v>
       </c>
       <c r="R45" t="n">
-        <v>7018111</v>
+        <v>7018088</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5093,7 +5093,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127025227</v>
+        <v>127025231</v>
       </c>
       <c r="B46" t="n">
         <v>98442</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609242</v>
+        <v>609305</v>
       </c>
       <c r="R46" t="n">
-        <v>7018088</v>
+        <v>7018111</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6435,7 +6435,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127025212</v>
+        <v>127025238</v>
       </c>
       <c r="B58" t="n">
         <v>98442</v>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609307</v>
+        <v>609526</v>
       </c>
       <c r="R58" t="n">
-        <v>7018143</v>
+        <v>7018059</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6546,7 +6546,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127025238</v>
+        <v>127025212</v>
       </c>
       <c r="B59" t="n">
         <v>98442</v>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609526</v>
+        <v>609307</v>
       </c>
       <c r="R59" t="n">
-        <v>7018059</v>
+        <v>7018143</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -5653,37 +5653,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025229</v>
+        <v>127025210</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>91621</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609265</v>
+        <v>609310</v>
       </c>
       <c r="R51" t="n">
-        <v>7018132</v>
+        <v>7018130</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127025210</v>
+        <v>127025211</v>
       </c>
       <c r="B52" t="n">
-        <v>91621</v>
+        <v>91325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609310</v>
+        <v>609316</v>
       </c>
       <c r="R52" t="n">
-        <v>7018130</v>
+        <v>7018135</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5875,37 +5875,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127025211</v>
+        <v>127025229</v>
       </c>
       <c r="B53" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609316</v>
+        <v>609265</v>
       </c>
       <c r="R53" t="n">
-        <v>7018135</v>
+        <v>7018132</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -4208,7 +4208,7 @@
         <v>127025234</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>127025224</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>127025225</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>127025209</v>
       </c>
       <c r="B41" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127025233</v>
       </c>
       <c r="B42" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>127025218</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>127025226</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127025227</v>
+        <v>127025231</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609242</v>
+        <v>609305</v>
       </c>
       <c r="R45" t="n">
-        <v>7018088</v>
+        <v>7018111</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5093,10 +5093,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127025231</v>
+        <v>127025227</v>
       </c>
       <c r="B46" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609305</v>
+        <v>609242</v>
       </c>
       <c r="R46" t="n">
-        <v>7018111</v>
+        <v>7018088</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5207,7 +5207,7 @@
         <v>127025221</v>
       </c>
       <c r="B47" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>127025214</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>127025230</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>127025236</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,37 +5653,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025210</v>
+        <v>127025229</v>
       </c>
       <c r="B51" t="n">
-        <v>91621</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609310</v>
+        <v>609265</v>
       </c>
       <c r="R51" t="n">
-        <v>7018130</v>
+        <v>7018132</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127025211</v>
+        <v>127025210</v>
       </c>
       <c r="B52" t="n">
-        <v>91325</v>
+        <v>91622</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609316</v>
+        <v>609310</v>
       </c>
       <c r="R52" t="n">
-        <v>7018135</v>
+        <v>7018130</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5875,37 +5875,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127025229</v>
+        <v>127025211</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609265</v>
+        <v>609316</v>
       </c>
       <c r="R53" t="n">
-        <v>7018132</v>
+        <v>7018135</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5989,7 +5989,7 @@
         <v>127025222</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>127025228</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>127025219</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>127025215</v>
       </c>
       <c r="B57" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>127025238</v>
       </c>
       <c r="B58" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>127025212</v>
       </c>
       <c r="B59" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>127025216</v>
       </c>
       <c r="B60" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>127025232</v>
       </c>
       <c r="B61" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>127025217</v>
       </c>
       <c r="B62" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>127025213</v>
       </c>
       <c r="B63" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>127025235</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -5431,7 +5431,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025230</v>
+        <v>127025236</v>
       </c>
       <c r="B49" t="n">
         <v>98443</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609292</v>
+        <v>609519</v>
       </c>
       <c r="R49" t="n">
-        <v>7018117</v>
+        <v>7018075</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5542,7 +5542,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025236</v>
+        <v>127025230</v>
       </c>
       <c r="B50" t="n">
         <v>98443</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5581,13 +5581,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609519</v>
+        <v>609292</v>
       </c>
       <c r="R50" t="n">
-        <v>7018075</v>
+        <v>7018117</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127025210</v>
+        <v>127025211</v>
       </c>
       <c r="B52" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609310</v>
+        <v>609316</v>
       </c>
       <c r="R52" t="n">
-        <v>7018130</v>
+        <v>7018135</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5875,10 +5875,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127025211</v>
+        <v>127025210</v>
       </c>
       <c r="B53" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5886,21 +5886,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609316</v>
+        <v>609310</v>
       </c>
       <c r="R53" t="n">
-        <v>7018135</v>
+        <v>7018130</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -4208,7 +4208,7 @@
         <v>127025234</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>127025224</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>127025225</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4538,10 +4538,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127025209</v>
+        <v>127025218</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>609319</v>
+        <v>609180</v>
       </c>
       <c r="R41" t="n">
-        <v>7018124</v>
+        <v>7018103</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4652,7 +4652,7 @@
         <v>127025233</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127025218</v>
+        <v>127025209</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>609180</v>
+        <v>609319</v>
       </c>
       <c r="R43" t="n">
-        <v>7018103</v>
+        <v>7018124</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4874,7 +4874,7 @@
         <v>127025226</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>127025231</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>127025227</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127025221</v>
+        <v>127025214</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609216</v>
+        <v>609289</v>
       </c>
       <c r="R47" t="n">
-        <v>7018027</v>
+        <v>7018140</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5288,7 +5288,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Stort antal plantor inom ca 4 m</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5315,10 +5320,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025214</v>
+        <v>127025221</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5345,7 +5350,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5354,10 +5359,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609289</v>
+        <v>609216</v>
       </c>
       <c r="R48" t="n">
-        <v>7018140</v>
+        <v>7018027</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5389,7 +5394,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5399,12 +5404,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Stort antal plantor inom ca 4 m</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5431,10 +5431,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025236</v>
+        <v>127025230</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609519</v>
+        <v>609292</v>
       </c>
       <c r="R49" t="n">
-        <v>7018075</v>
+        <v>7018117</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5542,10 +5542,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025230</v>
+        <v>127025236</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5581,13 +5581,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609292</v>
+        <v>609519</v>
       </c>
       <c r="R50" t="n">
-        <v>7018117</v>
+        <v>7018075</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5656,7 +5656,7 @@
         <v>127025229</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5764,10 +5764,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127025211</v>
+        <v>127025210</v>
       </c>
       <c r="B52" t="n">
-        <v>91326</v>
+        <v>91626</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609316</v>
+        <v>609310</v>
       </c>
       <c r="R52" t="n">
-        <v>7018135</v>
+        <v>7018130</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5875,10 +5875,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127025210</v>
+        <v>127025211</v>
       </c>
       <c r="B53" t="n">
-        <v>91622</v>
+        <v>91330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5886,21 +5886,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609310</v>
+        <v>609316</v>
       </c>
       <c r="R53" t="n">
-        <v>7018130</v>
+        <v>7018135</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5986,10 +5986,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127025222</v>
+        <v>127025228</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609232</v>
+        <v>609266</v>
       </c>
       <c r="R54" t="n">
-        <v>7018046</v>
+        <v>7018108</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,10 +6097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127025228</v>
+        <v>127025222</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609266</v>
+        <v>609232</v>
       </c>
       <c r="R55" t="n">
-        <v>7018108</v>
+        <v>7018046</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,7 +6211,7 @@
         <v>127025219</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>127025215</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>127025238</v>
       </c>
       <c r="B58" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>127025212</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>127025216</v>
       </c>
       <c r="B60" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>127025232</v>
       </c>
       <c r="B61" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>127025217</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>127025213</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>127025235</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 19208-2025 artfynd.xlsx
+++ b/artfynd/A 19208-2025 artfynd.xlsx
@@ -4538,7 +4538,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127025218</v>
+        <v>127025209</v>
       </c>
       <c r="B41" t="n">
         <v>98447</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>609180</v>
+        <v>609319</v>
       </c>
       <c r="R41" t="n">
-        <v>7018103</v>
+        <v>7018124</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4760,7 +4760,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127025209</v>
+        <v>127025218</v>
       </c>
       <c r="B43" t="n">
         <v>98447</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>609319</v>
+        <v>609180</v>
       </c>
       <c r="R43" t="n">
-        <v>7018124</v>
+        <v>7018103</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,7 +5204,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127025214</v>
+        <v>127025221</v>
       </c>
       <c r="B47" t="n">
         <v>98447</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609289</v>
+        <v>609216</v>
       </c>
       <c r="R47" t="n">
-        <v>7018140</v>
+        <v>7018027</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5288,12 +5288,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Stort antal plantor inom ca 4 m</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5320,7 +5315,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025221</v>
+        <v>127025214</v>
       </c>
       <c r="B48" t="n">
         <v>98447</v>
@@ -5350,7 +5345,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609216</v>
+        <v>609289</v>
       </c>
       <c r="R48" t="n">
-        <v>7018027</v>
+        <v>7018140</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5394,7 +5389,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5404,7 +5399,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Stort antal plantor inom ca 4 m</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5653,37 +5653,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025229</v>
+        <v>127025211</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609265</v>
+        <v>609316</v>
       </c>
       <c r="R51" t="n">
-        <v>7018132</v>
+        <v>7018135</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5875,37 +5875,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127025211</v>
+        <v>127025229</v>
       </c>
       <c r="B53" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609316</v>
+        <v>609265</v>
       </c>
       <c r="R53" t="n">
-        <v>7018135</v>
+        <v>7018132</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5986,7 +5986,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127025228</v>
+        <v>127025222</v>
       </c>
       <c r="B54" t="n">
         <v>98447</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609266</v>
+        <v>609232</v>
       </c>
       <c r="R54" t="n">
-        <v>7018108</v>
+        <v>7018046</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,7 +6097,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127025222</v>
+        <v>127025228</v>
       </c>
       <c r="B55" t="n">
         <v>98447</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609232</v>
+        <v>609266</v>
       </c>
       <c r="R55" t="n">
-        <v>7018046</v>
+        <v>7018108</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
